--- a/Spacecrafts_site_1000/2024-178B_Dragon_Trunk.xlsx
+++ b/Spacecrafts_site_1000/2024-178B_Dragon_Trunk.xlsx
@@ -452,1315 +452,1315 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114.35</v>
+        <v>0.32</v>
       </c>
       <c r="B2" t="n">
-        <v>25955</v>
+        <v>38449</v>
       </c>
       <c r="C2" t="n">
-        <v>118.18</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>28284</v>
+        <v>28404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100.14</v>
+        <v>1.18</v>
       </c>
       <c r="B3" t="n">
-        <v>46646</v>
+        <v>37899</v>
       </c>
       <c r="C3" t="n">
-        <v>96.18000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="D3" t="n">
-        <v>28229</v>
+        <v>25183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19.89</v>
+        <v>1.69</v>
       </c>
       <c r="B4" t="n">
-        <v>29337</v>
+        <v>40037</v>
       </c>
       <c r="C4" t="n">
-        <v>19.66</v>
+        <v>1.3</v>
       </c>
       <c r="D4" t="n">
-        <v>25034</v>
+        <v>23899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108.89</v>
+        <v>1.96</v>
       </c>
       <c r="B5" t="n">
-        <v>38644</v>
+        <v>40532</v>
       </c>
       <c r="C5" t="n">
-        <v>103.52</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>28318</v>
+        <v>23922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112.45</v>
+        <v>2.75</v>
       </c>
       <c r="B6" t="n">
-        <v>28560</v>
+        <v>36277</v>
       </c>
       <c r="C6" t="n">
-        <v>115.31</v>
+        <v>1.03</v>
       </c>
       <c r="D6" t="n">
-        <v>24956</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7.04</v>
+        <v>2.82</v>
       </c>
       <c r="B7" t="n">
-        <v>26232</v>
+        <v>39383</v>
       </c>
       <c r="C7" t="n">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>28311</v>
+        <v>23782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109.8</v>
+        <v>2.93</v>
       </c>
       <c r="B8" t="n">
-        <v>34948</v>
+        <v>38077</v>
       </c>
       <c r="C8" t="n">
-        <v>114.29</v>
+        <v>5.78</v>
       </c>
       <c r="D8" t="n">
-        <v>25047</v>
+        <v>24839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112.86</v>
+        <v>3.65</v>
       </c>
       <c r="B9" t="n">
-        <v>24793</v>
+        <v>36693</v>
       </c>
       <c r="C9" t="n">
-        <v>111.98</v>
+        <v>1.69</v>
       </c>
       <c r="D9" t="n">
-        <v>23837</v>
+        <v>24941</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95.95</v>
+        <v>3.74</v>
       </c>
       <c r="B10" t="n">
-        <v>37873</v>
+        <v>39027</v>
       </c>
       <c r="C10" t="n">
-        <v>92.81</v>
+        <v>7.93</v>
       </c>
       <c r="D10" t="n">
-        <v>24930</v>
+        <v>23906</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>3.78</v>
       </c>
       <c r="B11" t="n">
-        <v>27185</v>
+        <v>36968</v>
       </c>
       <c r="C11" t="n">
-        <v>0.16</v>
+        <v>1.13</v>
       </c>
       <c r="D11" t="n">
-        <v>23899</v>
+        <v>28331</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97.5</v>
+        <v>4.55</v>
       </c>
       <c r="B12" t="n">
-        <v>42900</v>
+        <v>35800</v>
       </c>
       <c r="C12" t="n">
-        <v>100.25</v>
+        <v>15.67</v>
       </c>
       <c r="D12" t="n">
-        <v>28404</v>
+        <v>24958</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>86.23999999999999</v>
+        <v>5.05</v>
       </c>
       <c r="B13" t="n">
-        <v>25550</v>
+        <v>36263</v>
       </c>
       <c r="C13" t="n">
-        <v>85.87</v>
+        <v>3.72</v>
       </c>
       <c r="D13" t="n">
-        <v>25016</v>
+        <v>28475</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>90.47</v>
+        <v>5.83</v>
       </c>
       <c r="B14" t="n">
-        <v>28013</v>
+        <v>36002</v>
       </c>
       <c r="C14" t="n">
-        <v>91.59999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="D14" t="n">
-        <v>24041</v>
+        <v>28410</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>92.95999999999999</v>
+        <v>6.15</v>
       </c>
       <c r="B15" t="n">
-        <v>28389</v>
+        <v>36988</v>
       </c>
       <c r="C15" t="n">
-        <v>95.84</v>
+        <v>3.67</v>
       </c>
       <c r="D15" t="n">
-        <v>23849</v>
+        <v>24893</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>93.52</v>
+        <v>6.58</v>
       </c>
       <c r="B16" t="n">
-        <v>30030</v>
+        <v>35788</v>
       </c>
       <c r="C16" t="n">
-        <v>96.26000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="D16" t="n">
-        <v>23902</v>
+        <v>23941</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106.78</v>
+        <v>7.54</v>
       </c>
       <c r="B17" t="n">
-        <v>46001</v>
+        <v>34669</v>
       </c>
       <c r="C17" t="n">
-        <v>106.6</v>
+        <v>5.7</v>
       </c>
       <c r="D17" t="n">
-        <v>13.41</v>
+        <v>25005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>93.81999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="B18" t="n">
-        <v>33114</v>
+        <v>35551</v>
       </c>
       <c r="C18" t="n">
-        <v>94.05</v>
+        <v>16.41</v>
       </c>
       <c r="D18" t="n">
-        <v>24084</v>
+        <v>25020</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>90.90000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="B19" t="n">
-        <v>24509</v>
+        <v>35839</v>
       </c>
       <c r="C19" t="n">
-        <v>93.16</v>
+        <v>8.24</v>
       </c>
       <c r="D19" t="n">
-        <v>24029</v>
+        <v>28338</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>93.59999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="B20" t="n">
-        <v>30362</v>
+        <v>33519</v>
       </c>
       <c r="C20" t="n">
-        <v>90.52</v>
+        <v>9.57</v>
       </c>
       <c r="D20" t="n">
-        <v>24048</v>
+        <v>28353</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109.63</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="B21" t="n">
-        <v>33869</v>
+        <v>34362</v>
       </c>
       <c r="C21" t="n">
-        <v>109.14</v>
+        <v>9.42</v>
       </c>
       <c r="D21" t="n">
-        <v>25013</v>
+        <v>25058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113.42</v>
+        <v>8.84</v>
       </c>
       <c r="B22" t="n">
-        <v>23966</v>
+        <v>33988</v>
       </c>
       <c r="C22" t="n">
-        <v>114.98</v>
+        <v>16.15</v>
       </c>
       <c r="D22" t="n">
-        <v>28314</v>
+        <v>24996</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>164.89</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="B23" t="n">
-        <v>26772</v>
+        <v>34940</v>
       </c>
       <c r="C23" t="n">
-        <v>166.42</v>
+        <v>9.19</v>
       </c>
       <c r="D23" t="n">
-        <v>23932</v>
+        <v>25102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108.32</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="B24" t="n">
-        <v>40339</v>
+        <v>34430</v>
       </c>
       <c r="C24" t="n">
-        <v>109.78</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>24949</v>
+        <v>25101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102.02</v>
+        <v>9.44</v>
       </c>
       <c r="B25" t="n">
-        <v>47966</v>
+        <v>34219</v>
       </c>
       <c r="C25" t="n">
-        <v>103.59</v>
+        <v>4.89</v>
       </c>
       <c r="D25" t="n">
-        <v>13.76</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96.15000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="B26" t="n">
-        <v>37551</v>
+        <v>33398</v>
       </c>
       <c r="C26" t="n">
-        <v>96.63</v>
+        <v>6.65</v>
       </c>
       <c r="D26" t="n">
-        <v>28150</v>
+        <v>28350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101.38</v>
+        <v>11.31</v>
       </c>
       <c r="B27" t="n">
-        <v>47164</v>
+        <v>32490</v>
       </c>
       <c r="C27" t="n">
-        <v>101.47</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>24984</v>
+        <v>28099</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114.21</v>
+        <v>12.33</v>
       </c>
       <c r="B28" t="n">
-        <v>26023</v>
+        <v>31274</v>
       </c>
       <c r="C28" t="n">
-        <v>117.2</v>
+        <v>21.94</v>
       </c>
       <c r="D28" t="n">
-        <v>23952</v>
+        <v>24986</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>98.68000000000001</v>
+        <v>14.14</v>
       </c>
       <c r="B29" t="n">
-        <v>44298</v>
+        <v>25981</v>
       </c>
       <c r="C29" t="n">
-        <v>95.04000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="D29" t="n">
-        <v>25059</v>
+        <v>24803</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104.51</v>
+        <v>14.32</v>
       </c>
       <c r="B30" t="n">
-        <v>49671</v>
+        <v>27372</v>
       </c>
       <c r="C30" t="n">
-        <v>101.07</v>
+        <v>12.48</v>
       </c>
       <c r="D30" t="n">
-        <v>23814</v>
+        <v>25045</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>39.78</v>
+        <v>14.34</v>
       </c>
       <c r="B31" t="n">
-        <v>26914</v>
+        <v>30753</v>
       </c>
       <c r="C31" t="n">
-        <v>40.13</v>
+        <v>16.51</v>
       </c>
       <c r="D31" t="n">
-        <v>25027</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97.28</v>
+        <v>14.52</v>
       </c>
       <c r="B32" t="n">
-        <v>43526</v>
+        <v>30075</v>
       </c>
       <c r="C32" t="n">
-        <v>98.34</v>
+        <v>5.66</v>
       </c>
       <c r="D32" t="n">
-        <v>24030</v>
+        <v>28410</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109.01</v>
+        <v>14.95</v>
       </c>
       <c r="B33" t="n">
-        <v>38233</v>
+        <v>27542</v>
       </c>
       <c r="C33" t="n">
-        <v>108.05</v>
+        <v>20.58</v>
       </c>
       <c r="D33" t="n">
-        <v>28212</v>
+        <v>28289</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96.31</v>
+        <v>15.27</v>
       </c>
       <c r="B34" t="n">
-        <v>41980</v>
+        <v>32397</v>
       </c>
       <c r="C34" t="n">
-        <v>95.97</v>
+        <v>23.17</v>
       </c>
       <c r="D34" t="n">
-        <v>23920</v>
+        <v>24109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105.75</v>
+        <v>15.98</v>
       </c>
       <c r="B35" t="n">
-        <v>44873</v>
+        <v>28708</v>
       </c>
       <c r="C35" t="n">
-        <v>105.58</v>
+        <v>19.24</v>
       </c>
       <c r="D35" t="n">
-        <v>23879</v>
+        <v>25012</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111.5</v>
+        <v>16.16</v>
       </c>
       <c r="B36" t="n">
-        <v>31173</v>
+        <v>29103</v>
       </c>
       <c r="C36" t="n">
-        <v>107.32</v>
+        <v>14.87</v>
       </c>
       <c r="D36" t="n">
-        <v>25163</v>
+        <v>28509</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111.51</v>
+        <v>16.59</v>
       </c>
       <c r="B37" t="n">
-        <v>31815</v>
+        <v>26744</v>
       </c>
       <c r="C37" t="n">
-        <v>115.04</v>
+        <v>12.51</v>
       </c>
       <c r="D37" t="n">
-        <v>24964</v>
+        <v>28401</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7.25</v>
+        <v>16.7</v>
       </c>
       <c r="B38" t="n">
-        <v>24789</v>
+        <v>24664</v>
       </c>
       <c r="C38" t="n">
-        <v>7.12</v>
+        <v>19.85</v>
       </c>
       <c r="D38" t="n">
-        <v>24973</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>60.41</v>
+        <v>16.94</v>
       </c>
       <c r="B39" t="n">
-        <v>26907</v>
+        <v>26972</v>
       </c>
       <c r="C39" t="n">
-        <v>62.14</v>
+        <v>11.5</v>
       </c>
       <c r="D39" t="n">
-        <v>28141</v>
+        <v>23997</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112.82</v>
+        <v>17.37</v>
       </c>
       <c r="B40" t="n">
-        <v>28434</v>
+        <v>26331</v>
       </c>
       <c r="C40" t="n">
-        <v>114.82</v>
+        <v>19.77</v>
       </c>
       <c r="D40" t="n">
-        <v>23962</v>
+        <v>24043</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101.05</v>
+        <v>17.97</v>
       </c>
       <c r="B41" t="n">
-        <v>48780</v>
+        <v>27206</v>
       </c>
       <c r="C41" t="n">
-        <v>99.84</v>
+        <v>25.12</v>
       </c>
       <c r="D41" t="n">
-        <v>23708</v>
+        <v>28212</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>92.3</v>
+        <v>18.44</v>
       </c>
       <c r="B42" t="n">
-        <v>30451</v>
+        <v>25989</v>
       </c>
       <c r="C42" t="n">
-        <v>89.83</v>
+        <v>18.9</v>
       </c>
       <c r="D42" t="n">
-        <v>13.24</v>
+        <v>28143</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>100.54</v>
+        <v>18.7</v>
       </c>
       <c r="B43" t="n">
-        <v>47648</v>
+        <v>25534</v>
       </c>
       <c r="C43" t="n">
-        <v>102.5</v>
+        <v>28.45</v>
       </c>
       <c r="D43" t="n">
-        <v>13.76</v>
+        <v>24052</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112.29</v>
+        <v>18.74</v>
       </c>
       <c r="B44" t="n">
-        <v>27809</v>
+        <v>27576</v>
       </c>
       <c r="C44" t="n">
-        <v>108.84</v>
+        <v>12.59</v>
       </c>
       <c r="D44" t="n">
-        <v>28177</v>
+        <v>25024</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122.52</v>
+        <v>19.17</v>
       </c>
       <c r="B45" t="n">
-        <v>22503</v>
+        <v>26784</v>
       </c>
       <c r="C45" t="n">
-        <v>123.8</v>
+        <v>13.85</v>
       </c>
       <c r="D45" t="n">
-        <v>25019</v>
+        <v>23926</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>150.94</v>
+        <v>19.25</v>
       </c>
       <c r="B46" t="n">
-        <v>24006</v>
+        <v>26448</v>
       </c>
       <c r="C46" t="n">
-        <v>147.3</v>
+        <v>13.79</v>
       </c>
       <c r="D46" t="n">
-        <v>23749</v>
+        <v>24792</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112</v>
+        <v>20.43</v>
       </c>
       <c r="B47" t="n">
-        <v>28506</v>
+        <v>24638</v>
       </c>
       <c r="C47" t="n">
-        <v>115.69</v>
+        <v>28.47</v>
       </c>
       <c r="D47" t="n">
-        <v>25090</v>
+        <v>28333</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103.77</v>
+        <v>20.87</v>
       </c>
       <c r="B48" t="n">
-        <v>48736</v>
+        <v>23899</v>
       </c>
       <c r="C48" t="n">
-        <v>103.56</v>
+        <v>19.86</v>
       </c>
       <c r="D48" t="n">
-        <v>25003</v>
+        <v>24871</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>107.91</v>
+        <v>21.29</v>
       </c>
       <c r="B49" t="n">
-        <v>41614</v>
+        <v>23386</v>
       </c>
       <c r="C49" t="n">
-        <v>103.94</v>
+        <v>21.83</v>
       </c>
       <c r="D49" t="n">
-        <v>23936</v>
+        <v>23937</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>63.84</v>
+        <v>21.88</v>
       </c>
       <c r="B50" t="n">
-        <v>25030</v>
+        <v>25302</v>
       </c>
       <c r="C50" t="n">
-        <v>63.93</v>
+        <v>18.69</v>
       </c>
       <c r="D50" t="n">
-        <v>24076</v>
+        <v>28339</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>92.75</v>
+        <v>22.26</v>
       </c>
       <c r="B51" t="n">
-        <v>29828</v>
+        <v>24079</v>
       </c>
       <c r="C51" t="n">
-        <v>95.28</v>
+        <v>26.13</v>
       </c>
       <c r="D51" t="n">
-        <v>23950</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>107.65</v>
+        <v>22.73</v>
       </c>
       <c r="B52" t="n">
-        <v>40599</v>
+        <v>25595</v>
       </c>
       <c r="C52" t="n">
-        <v>110.3</v>
+        <v>20.51</v>
       </c>
       <c r="D52" t="n">
-        <v>24995</v>
+        <v>25042</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129.11</v>
+        <v>23.49</v>
       </c>
       <c r="B53" t="n">
-        <v>25409</v>
+        <v>21257</v>
       </c>
       <c r="C53" t="n">
-        <v>130.83</v>
+        <v>20.72</v>
       </c>
       <c r="D53" t="n">
-        <v>24880</v>
+        <v>28283</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112.86</v>
+        <v>23.68</v>
       </c>
       <c r="B54" t="n">
-        <v>26717</v>
+        <v>22727</v>
       </c>
       <c r="C54" t="n">
-        <v>117.85</v>
+        <v>27.62</v>
       </c>
       <c r="D54" t="n">
-        <v>13.36</v>
+        <v>23941</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>114.23</v>
+        <v>23.81</v>
       </c>
       <c r="B55" t="n">
-        <v>24342</v>
+        <v>23773</v>
       </c>
       <c r="C55" t="n">
-        <v>117.59</v>
+        <v>18.12</v>
       </c>
       <c r="D55" t="n">
-        <v>28324</v>
+        <v>24981</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>72.16</v>
+        <v>24.66</v>
       </c>
       <c r="B56" t="n">
-        <v>24199</v>
+        <v>23506</v>
       </c>
       <c r="C56" t="n">
-        <v>72.23999999999999</v>
+        <v>29.8</v>
       </c>
       <c r="D56" t="n">
-        <v>23897</v>
+        <v>23910</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>96.33</v>
+        <v>27.05</v>
       </c>
       <c r="B57" t="n">
-        <v>38388</v>
+        <v>22905</v>
       </c>
       <c r="C57" t="n">
-        <v>95.14</v>
+        <v>28.27</v>
       </c>
       <c r="D57" t="n">
-        <v>25143</v>
+        <v>23893</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>93</v>
+        <v>27.65</v>
       </c>
       <c r="B58" t="n">
-        <v>29712</v>
+        <v>22642</v>
       </c>
       <c r="C58" t="n">
-        <v>93.61</v>
+        <v>32.58</v>
       </c>
       <c r="D58" t="n">
-        <v>23840</v>
+        <v>28188</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111.73</v>
+        <v>28.35</v>
       </c>
       <c r="B59" t="n">
-        <v>28073</v>
+        <v>25484</v>
       </c>
       <c r="C59" t="n">
-        <v>111.35</v>
+        <v>36.92</v>
       </c>
       <c r="D59" t="n">
-        <v>23779</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>90.86</v>
+        <v>28.5</v>
       </c>
       <c r="B60" t="n">
-        <v>27169</v>
+        <v>24265</v>
       </c>
       <c r="C60" t="n">
-        <v>88.5</v>
+        <v>15.77</v>
       </c>
       <c r="D60" t="n">
-        <v>23864</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>91.72</v>
+        <v>28.89</v>
       </c>
       <c r="B61" t="n">
-        <v>23861</v>
+        <v>24488</v>
       </c>
       <c r="C61" t="n">
-        <v>89.84999999999999</v>
+        <v>28.37</v>
       </c>
       <c r="D61" t="n">
-        <v>24012</v>
+        <v>24907</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>114.91</v>
+        <v>29</v>
       </c>
       <c r="B62" t="n">
-        <v>27131</v>
+        <v>20634</v>
       </c>
       <c r="C62" t="n">
-        <v>117.99</v>
+        <v>29.3</v>
       </c>
       <c r="D62" t="n">
-        <v>23898</v>
+        <v>23986</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102.15</v>
+        <v>29.78</v>
       </c>
       <c r="B63" t="n">
-        <v>50808</v>
+        <v>23085</v>
       </c>
       <c r="C63" t="n">
-        <v>103.53</v>
+        <v>22.84</v>
       </c>
       <c r="D63" t="n">
-        <v>28309</v>
+        <v>23934</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113.69</v>
+        <v>29.86</v>
       </c>
       <c r="B64" t="n">
-        <v>25272</v>
+        <v>21933</v>
       </c>
       <c r="C64" t="n">
-        <v>109.44</v>
+        <v>25.11</v>
       </c>
       <c r="D64" t="n">
-        <v>28410</v>
+        <v>23881</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>105.29</v>
+        <v>30.01</v>
       </c>
       <c r="B65" t="n">
-        <v>46031</v>
+        <v>24019</v>
       </c>
       <c r="C65" t="n">
-        <v>108.33</v>
+        <v>31.95</v>
       </c>
       <c r="D65" t="n">
-        <v>25063</v>
+        <v>24066</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>98.83</v>
+        <v>30.33</v>
       </c>
       <c r="B66" t="n">
-        <v>42767</v>
+        <v>23217</v>
       </c>
       <c r="C66" t="n">
-        <v>100.76</v>
+        <v>35.56</v>
       </c>
       <c r="D66" t="n">
-        <v>23870</v>
+        <v>28278</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>101.91</v>
+        <v>30.59</v>
       </c>
       <c r="B67" t="n">
-        <v>49252</v>
+        <v>22852</v>
       </c>
       <c r="C67" t="n">
-        <v>100.58</v>
+        <v>30.21</v>
       </c>
       <c r="D67" t="n">
-        <v>25055</v>
+        <v>23907</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>114.08</v>
+        <v>30.99</v>
       </c>
       <c r="B68" t="n">
-        <v>29167</v>
+        <v>25781</v>
       </c>
       <c r="C68" t="n">
-        <v>117.33</v>
+        <v>30.65</v>
       </c>
       <c r="D68" t="n">
-        <v>24966</v>
+        <v>28409</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>108.54</v>
+        <v>31.14</v>
       </c>
       <c r="B69" t="n">
-        <v>38073</v>
+        <v>22379</v>
       </c>
       <c r="C69" t="n">
-        <v>109.68</v>
+        <v>31.01</v>
       </c>
       <c r="D69" t="n">
-        <v>13.24</v>
+        <v>25151</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>95.97</v>
+        <v>31.89</v>
       </c>
       <c r="B70" t="n">
-        <v>37878</v>
+        <v>22858</v>
       </c>
       <c r="C70" t="n">
-        <v>98.09</v>
+        <v>39.12</v>
       </c>
       <c r="D70" t="n">
-        <v>23966</v>
+        <v>24007</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>95.04000000000001</v>
+        <v>32.19</v>
       </c>
       <c r="B71" t="n">
-        <v>34666</v>
+        <v>22632</v>
       </c>
       <c r="C71" t="n">
-        <v>95.11</v>
+        <v>28.75</v>
       </c>
       <c r="D71" t="n">
-        <v>23831</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96.08</v>
+        <v>33</v>
       </c>
       <c r="B72" t="n">
-        <v>38687</v>
+        <v>23105</v>
       </c>
       <c r="C72" t="n">
-        <v>94.72</v>
+        <v>27.19</v>
       </c>
       <c r="D72" t="n">
-        <v>28301</v>
+        <v>28368</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>100.99</v>
+        <v>33.03</v>
       </c>
       <c r="B73" t="n">
-        <v>50417</v>
+        <v>24468</v>
       </c>
       <c r="C73" t="n">
-        <v>103.36</v>
+        <v>39.38</v>
       </c>
       <c r="D73" t="n">
-        <v>25024</v>
+        <v>23890</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>97.62</v>
+        <v>33.2</v>
       </c>
       <c r="B74" t="n">
-        <v>41104</v>
+        <v>24966</v>
       </c>
       <c r="C74" t="n">
-        <v>95.23999999999999</v>
+        <v>35.54</v>
       </c>
       <c r="D74" t="n">
-        <v>23941</v>
+        <v>28145</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>114.32</v>
+        <v>33.52</v>
       </c>
       <c r="B75" t="n">
-        <v>25332</v>
+        <v>22544</v>
       </c>
       <c r="C75" t="n">
-        <v>113.94</v>
+        <v>29.72</v>
       </c>
       <c r="D75" t="n">
-        <v>28201</v>
+        <v>23933</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15.93</v>
+        <v>33.57</v>
       </c>
       <c r="B76" t="n">
-        <v>25688</v>
+        <v>23754</v>
       </c>
       <c r="C76" t="n">
-        <v>16.04</v>
+        <v>30.83</v>
       </c>
       <c r="D76" t="n">
-        <v>25192</v>
+        <v>28333</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>114.88</v>
+        <v>33.68</v>
       </c>
       <c r="B77" t="n">
-        <v>25166</v>
+        <v>25672</v>
       </c>
       <c r="C77" t="n">
-        <v>113.21</v>
+        <v>36.53</v>
       </c>
       <c r="D77" t="n">
-        <v>24021</v>
+        <v>28281</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104.92</v>
+        <v>33.77</v>
       </c>
       <c r="B78" t="n">
-        <v>51347</v>
+        <v>23020</v>
       </c>
       <c r="C78" t="n">
-        <v>103.43</v>
+        <v>40.11</v>
       </c>
       <c r="D78" t="n">
-        <v>23976</v>
+        <v>25040</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>108.81</v>
+        <v>34.97</v>
       </c>
       <c r="B79" t="n">
-        <v>38943</v>
+        <v>21035</v>
       </c>
       <c r="C79" t="n">
-        <v>105.32</v>
+        <v>29.66</v>
       </c>
       <c r="D79" t="n">
-        <v>13.76</v>
+        <v>28291</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>103.27</v>
+        <v>35.76</v>
       </c>
       <c r="B80" t="n">
-        <v>46870</v>
+        <v>22106</v>
       </c>
       <c r="C80" t="n">
-        <v>107.21</v>
+        <v>32.14</v>
       </c>
       <c r="D80" t="n">
-        <v>23873</v>
+        <v>24885</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>110.58</v>
+        <v>36.42</v>
       </c>
       <c r="B81" t="n">
-        <v>34461</v>
+        <v>20810</v>
       </c>
       <c r="C81" t="n">
-        <v>114.41</v>
+        <v>37.16</v>
       </c>
       <c r="D81" t="n">
-        <v>28167</v>
+        <v>23913</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113.81</v>
+        <v>36.43</v>
       </c>
       <c r="B82" t="n">
-        <v>25080</v>
+        <v>22626</v>
       </c>
       <c r="C82" t="n">
-        <v>113.15</v>
+        <v>32.53</v>
       </c>
       <c r="D82" t="n">
-        <v>23842</v>
+        <v>23928</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110.7</v>
+        <v>36.61</v>
       </c>
       <c r="B83" t="n">
-        <v>29946</v>
+        <v>24737</v>
       </c>
       <c r="C83" t="n">
-        <v>110.55</v>
+        <v>39.56</v>
       </c>
       <c r="D83" t="n">
-        <v>28136</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96.48</v>
+        <v>36.61</v>
       </c>
       <c r="B84" t="n">
-        <v>41422</v>
+        <v>24261</v>
       </c>
       <c r="C84" t="n">
-        <v>96.19</v>
+        <v>31.32</v>
       </c>
       <c r="D84" t="n">
-        <v>24000</v>
+        <v>24926</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>92.19</v>
+        <v>36.68</v>
       </c>
       <c r="B85" t="n">
-        <v>27115</v>
+        <v>21195</v>
       </c>
       <c r="C85" t="n">
-        <v>93.42</v>
+        <v>45.85</v>
       </c>
       <c r="D85" t="n">
-        <v>25021</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>103.14</v>
+        <v>37.26</v>
       </c>
       <c r="B86" t="n">
-        <v>49401</v>
+        <v>26105</v>
       </c>
       <c r="C86" t="n">
-        <v>102.67</v>
+        <v>45.38</v>
       </c>
       <c r="D86" t="n">
-        <v>28359</v>
+        <v>28195</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113.1</v>
+        <v>37.75</v>
       </c>
       <c r="B87" t="n">
-        <v>27790</v>
+        <v>23798</v>
       </c>
       <c r="C87" t="n">
-        <v>111.93</v>
+        <v>36.2</v>
       </c>
       <c r="D87" t="n">
-        <v>24976</v>
+        <v>24161</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>104.56</v>
+        <v>37.84</v>
       </c>
       <c r="B88" t="n">
-        <v>46211</v>
+        <v>24343</v>
       </c>
       <c r="C88" t="n">
-        <v>105.16</v>
+        <v>36.28</v>
       </c>
       <c r="D88" t="n">
-        <v>23913</v>
+        <v>24883</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104.25</v>
+        <v>37.87</v>
       </c>
       <c r="B89" t="n">
-        <v>46567</v>
+        <v>24336</v>
       </c>
       <c r="C89" t="n">
-        <v>104.73</v>
+        <v>28.7</v>
       </c>
       <c r="D89" t="n">
-        <v>28379</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>99.25</v>
+        <v>38.72</v>
       </c>
       <c r="B90" t="n">
-        <v>45145</v>
+        <v>22341</v>
       </c>
       <c r="C90" t="n">
-        <v>99.81</v>
+        <v>48</v>
       </c>
       <c r="D90" t="n">
-        <v>23928</v>
+        <v>25155</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.52</v>
+        <v>38.73</v>
       </c>
       <c r="B91" t="n">
-        <v>26219</v>
+        <v>21814</v>
       </c>
       <c r="C91" t="n">
-        <v>0.64</v>
+        <v>38.87</v>
       </c>
       <c r="D91" t="n">
-        <v>25120</v>
+        <v>23952</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>98.09999999999999</v>
+        <v>38.86</v>
       </c>
       <c r="B92" t="n">
-        <v>42204</v>
+        <v>22193</v>
       </c>
       <c r="C92" t="n">
-        <v>95.97</v>
+        <v>39.5</v>
       </c>
       <c r="D92" t="n">
-        <v>13.76</v>
+        <v>28379</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>93.09</v>
+        <v>39.14</v>
       </c>
       <c r="B93" t="n">
-        <v>28147</v>
+        <v>23077</v>
       </c>
       <c r="C93" t="n">
-        <v>91.38</v>
+        <v>46.06</v>
       </c>
       <c r="D93" t="n">
-        <v>28342</v>
+        <v>23977</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>98.45</v>
+        <v>39.45</v>
       </c>
       <c r="B94" t="n">
-        <v>45663</v>
+        <v>25053</v>
       </c>
       <c r="C94" t="n">
-        <v>94.56</v>
+        <v>36.52</v>
       </c>
       <c r="D94" t="n">
-        <v>24980</v>
+        <v>25051</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>101.34</v>
+        <v>39.9</v>
       </c>
       <c r="B95" t="n">
-        <v>46229</v>
+        <v>22812</v>
       </c>
       <c r="C95" t="n">
-        <v>98.58</v>
+        <v>40.59</v>
       </c>
       <c r="D95" t="n">
         <v>13.41</v>
@@ -1768,2519 +1768,2519 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>142.6</v>
+        <v>40.68</v>
       </c>
       <c r="B96" t="n">
-        <v>25161</v>
+        <v>24176</v>
       </c>
       <c r="C96" t="n">
-        <v>142.31</v>
+        <v>52.39</v>
       </c>
       <c r="D96" t="n">
-        <v>23839</v>
+        <v>28273</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>52.84</v>
+        <v>40.79</v>
       </c>
       <c r="B97" t="n">
-        <v>26683</v>
+        <v>22815</v>
       </c>
       <c r="C97" t="n">
-        <v>53.82</v>
+        <v>39.01</v>
       </c>
       <c r="D97" t="n">
-        <v>13.24</v>
+        <v>28359</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>93.68000000000001</v>
+        <v>41.37</v>
       </c>
       <c r="B98" t="n">
-        <v>33329</v>
+        <v>21767</v>
       </c>
       <c r="C98" t="n">
-        <v>94.93000000000001</v>
+        <v>41.64</v>
       </c>
       <c r="D98" t="n">
-        <v>23835</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>104.46</v>
+        <v>42.09</v>
       </c>
       <c r="B99" t="n">
-        <v>50892</v>
+        <v>24820</v>
       </c>
       <c r="C99" t="n">
-        <v>102.16</v>
+        <v>48.55</v>
       </c>
       <c r="D99" t="n">
-        <v>24964</v>
+        <v>28353</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99.09999999999999</v>
+        <v>42.36</v>
       </c>
       <c r="B100" t="n">
-        <v>44476</v>
+        <v>23017</v>
       </c>
       <c r="C100" t="n">
-        <v>95.37</v>
+        <v>32.67</v>
       </c>
       <c r="D100" t="n">
-        <v>28247</v>
+        <v>24027</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>91.68000000000001</v>
+        <v>42.9</v>
       </c>
       <c r="B101" t="n">
-        <v>27817</v>
+        <v>24639</v>
       </c>
       <c r="C101" t="n">
-        <v>94.55</v>
+        <v>51.63</v>
       </c>
       <c r="D101" t="n">
-        <v>28358</v>
+        <v>24753</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>66.05</v>
+        <v>43.16</v>
       </c>
       <c r="B102" t="n">
-        <v>27044</v>
+        <v>23007</v>
       </c>
       <c r="C102" t="n">
-        <v>68.48</v>
+        <v>38.4</v>
       </c>
       <c r="D102" t="n">
-        <v>28186</v>
+        <v>25266</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>99.39</v>
+        <v>43.16</v>
       </c>
       <c r="B103" t="n">
-        <v>47277</v>
+        <v>24768</v>
       </c>
       <c r="C103" t="n">
-        <v>100.32</v>
+        <v>35.41</v>
       </c>
       <c r="D103" t="n">
-        <v>25009</v>
+        <v>23926</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>109.42</v>
+        <v>43.27</v>
       </c>
       <c r="B104" t="n">
-        <v>34511</v>
+        <v>24156</v>
       </c>
       <c r="C104" t="n">
-        <v>105.01</v>
+        <v>51.78</v>
       </c>
       <c r="D104" t="n">
-        <v>25081</v>
+        <v>28157</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>96.94</v>
+        <v>43.44</v>
       </c>
       <c r="B105" t="n">
-        <v>40001</v>
+        <v>23178</v>
       </c>
       <c r="C105" t="n">
-        <v>100.14</v>
+        <v>48.72</v>
       </c>
       <c r="D105" t="n">
-        <v>28318</v>
+        <v>23870</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>97.12</v>
+        <v>43.53</v>
       </c>
       <c r="B106" t="n">
-        <v>42305</v>
+        <v>21552</v>
       </c>
       <c r="C106" t="n">
-        <v>98.61</v>
+        <v>34.89</v>
       </c>
       <c r="D106" t="n">
-        <v>24941</v>
+        <v>23879</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>96.47</v>
+        <v>43.56</v>
       </c>
       <c r="B107" t="n">
-        <v>41705</v>
+        <v>22179</v>
       </c>
       <c r="C107" t="n">
-        <v>97.27</v>
+        <v>49.77</v>
       </c>
       <c r="D107" t="n">
-        <v>28323</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>111.64</v>
+        <v>43.57</v>
       </c>
       <c r="B108" t="n">
-        <v>29003</v>
+        <v>25388</v>
       </c>
       <c r="C108" t="n">
-        <v>114.31</v>
+        <v>50.3</v>
       </c>
       <c r="D108" t="n">
-        <v>28358</v>
+        <v>23924</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>30.07</v>
+        <v>44.05</v>
       </c>
       <c r="B109" t="n">
-        <v>25333</v>
+        <v>24314</v>
       </c>
       <c r="C109" t="n">
-        <v>31.76</v>
+        <v>48.83</v>
       </c>
       <c r="D109" t="n">
-        <v>23866</v>
+        <v>24001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>114.24</v>
+        <v>44.06</v>
       </c>
       <c r="B110" t="n">
-        <v>25475</v>
+        <v>21020</v>
       </c>
       <c r="C110" t="n">
-        <v>116.17</v>
+        <v>51.38</v>
       </c>
       <c r="D110" t="n">
-        <v>28302</v>
+        <v>24783</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>99.90000000000001</v>
+        <v>44.43</v>
       </c>
       <c r="B111" t="n">
-        <v>48147</v>
+        <v>20639</v>
       </c>
       <c r="C111" t="n">
-        <v>102.98</v>
+        <v>28.04</v>
       </c>
       <c r="D111" t="n">
-        <v>24951</v>
+        <v>23888</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>114.11</v>
+        <v>45.12</v>
       </c>
       <c r="B112" t="n">
-        <v>25469</v>
+        <v>21602</v>
       </c>
       <c r="C112" t="n">
-        <v>112.83</v>
+        <v>48.97</v>
       </c>
       <c r="D112" t="n">
-        <v>23821</v>
+        <v>25036</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>10.37</v>
+        <v>45.33</v>
       </c>
       <c r="B113" t="n">
-        <v>26275</v>
+        <v>21860</v>
       </c>
       <c r="C113" t="n">
-        <v>10.53</v>
+        <v>57.94</v>
       </c>
       <c r="D113" t="n">
-        <v>24933</v>
+        <v>28184</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>99.86</v>
+        <v>45.65</v>
       </c>
       <c r="B114" t="n">
-        <v>45840</v>
+        <v>22657</v>
       </c>
       <c r="C114" t="n">
-        <v>97.58</v>
+        <v>34.95</v>
       </c>
       <c r="D114" t="n">
-        <v>24085</v>
+        <v>23947</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>100.71</v>
+        <v>45.67</v>
       </c>
       <c r="B115" t="n">
-        <v>48319</v>
+        <v>23228</v>
       </c>
       <c r="C115" t="n">
-        <v>99.16</v>
+        <v>40.4</v>
       </c>
       <c r="D115" t="n">
-        <v>28255</v>
+        <v>28165</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>102.53</v>
+        <v>46.28</v>
       </c>
       <c r="B116" t="n">
-        <v>45098</v>
+        <v>21768</v>
       </c>
       <c r="C116" t="n">
-        <v>98.94</v>
+        <v>36.48</v>
       </c>
       <c r="D116" t="n">
-        <v>28266</v>
+        <v>24921</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>100.28</v>
+        <v>46.46</v>
       </c>
       <c r="B117" t="n">
-        <v>47705</v>
+        <v>23688</v>
       </c>
       <c r="C117" t="n">
-        <v>101.62</v>
+        <v>41.81</v>
       </c>
       <c r="D117" t="n">
-        <v>23887</v>
+        <v>23995</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>104.5</v>
+        <v>46.97</v>
       </c>
       <c r="B118" t="n">
-        <v>47527</v>
+        <v>19328</v>
       </c>
       <c r="C118" t="n">
-        <v>102.36</v>
+        <v>29.95</v>
       </c>
       <c r="D118" t="n">
-        <v>23849</v>
+        <v>25045</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>107.28</v>
+        <v>47.21</v>
       </c>
       <c r="B119" t="n">
-        <v>42378</v>
+        <v>24048</v>
       </c>
       <c r="C119" t="n">
-        <v>109.17</v>
+        <v>61.77</v>
       </c>
       <c r="D119" t="n">
-        <v>28391</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>112.83</v>
+        <v>47.41</v>
       </c>
       <c r="B120" t="n">
-        <v>27805</v>
+        <v>25134</v>
       </c>
       <c r="C120" t="n">
-        <v>108.03</v>
+        <v>42.72</v>
       </c>
       <c r="D120" t="n">
-        <v>24971</v>
+        <v>28501</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>103.56</v>
+        <v>47.52</v>
       </c>
       <c r="B121" t="n">
-        <v>49877</v>
+        <v>20513</v>
       </c>
       <c r="C121" t="n">
-        <v>101.07</v>
+        <v>46.03</v>
       </c>
       <c r="D121" t="n">
-        <v>25056</v>
+        <v>23824</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>103.79</v>
+        <v>47.9</v>
       </c>
       <c r="B122" t="n">
-        <v>49849</v>
+        <v>23279</v>
       </c>
       <c r="C122" t="n">
-        <v>105.09</v>
+        <v>45</v>
       </c>
       <c r="D122" t="n">
-        <v>24023</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>91.84</v>
+        <v>48.48</v>
       </c>
       <c r="B123" t="n">
-        <v>25619</v>
+        <v>21905</v>
       </c>
       <c r="C123" t="n">
-        <v>88.5</v>
+        <v>49.1</v>
       </c>
       <c r="D123" t="n">
-        <v>28283</v>
+        <v>25081</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>161.61</v>
+        <v>48.6</v>
       </c>
       <c r="B124" t="n">
-        <v>23625</v>
+        <v>23060</v>
       </c>
       <c r="C124" t="n">
-        <v>161.6</v>
+        <v>40.79</v>
       </c>
       <c r="D124" t="n">
-        <v>13.41</v>
+        <v>23829</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>90.28</v>
+        <v>48.73</v>
       </c>
       <c r="B125" t="n">
-        <v>26779</v>
+        <v>22824</v>
       </c>
       <c r="C125" t="n">
-        <v>86.18000000000001</v>
+        <v>46.91</v>
       </c>
       <c r="D125" t="n">
-        <v>28268</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>105.39</v>
+        <v>48.9</v>
       </c>
       <c r="B126" t="n">
-        <v>48246</v>
+        <v>22472</v>
       </c>
       <c r="C126" t="n">
-        <v>106.76</v>
+        <v>67.95</v>
       </c>
       <c r="D126" t="n">
-        <v>28373</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>92.62</v>
+        <v>49.27</v>
       </c>
       <c r="B127" t="n">
-        <v>29726</v>
+        <v>21153</v>
       </c>
       <c r="C127" t="n">
-        <v>94.73</v>
+        <v>45.42</v>
       </c>
       <c r="D127" t="n">
-        <v>24941</v>
+        <v>28349</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>97.83</v>
+        <v>49.33</v>
       </c>
       <c r="B128" t="n">
-        <v>42706</v>
+        <v>22529</v>
       </c>
       <c r="C128" t="n">
-        <v>100.84</v>
+        <v>31.45</v>
       </c>
       <c r="D128" t="n">
-        <v>24922</v>
+        <v>23982</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>102.92</v>
+        <v>49.46</v>
       </c>
       <c r="B129" t="n">
-        <v>47846</v>
+        <v>24423</v>
       </c>
       <c r="C129" t="n">
-        <v>104.63</v>
+        <v>62.61</v>
       </c>
       <c r="D129" t="n">
-        <v>24927</v>
+        <v>25050</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>148.05</v>
+        <v>49.5</v>
       </c>
       <c r="B130" t="n">
-        <v>23070</v>
+        <v>22305</v>
       </c>
       <c r="C130" t="n">
-        <v>152.73</v>
+        <v>52.49</v>
       </c>
       <c r="D130" t="n">
-        <v>24865</v>
+        <v>25122</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>94.02</v>
+        <v>49.68</v>
       </c>
       <c r="B131" t="n">
-        <v>32058</v>
+        <v>23457</v>
       </c>
       <c r="C131" t="n">
-        <v>97.08</v>
+        <v>37.06</v>
       </c>
       <c r="D131" t="n">
-        <v>23882</v>
+        <v>23994</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>112.64</v>
+        <v>50.49</v>
       </c>
       <c r="B132" t="n">
-        <v>26273</v>
+        <v>24776</v>
       </c>
       <c r="C132" t="n">
-        <v>113.94</v>
+        <v>44.37</v>
       </c>
       <c r="D132" t="n">
-        <v>28325</v>
+        <v>28154</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>103.89</v>
+        <v>50.84</v>
       </c>
       <c r="B133" t="n">
-        <v>48777</v>
+        <v>24393</v>
       </c>
       <c r="C133" t="n">
-        <v>103.33</v>
+        <v>45.26</v>
       </c>
       <c r="D133" t="n">
-        <v>28288</v>
+        <v>24987</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>101.63</v>
+        <v>50.95</v>
       </c>
       <c r="B134" t="n">
-        <v>51031</v>
+        <v>21618</v>
       </c>
       <c r="C134" t="n">
-        <v>97.65000000000001</v>
+        <v>50.37</v>
       </c>
       <c r="D134" t="n">
-        <v>24078</v>
+        <v>25187</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>98.22</v>
+        <v>51.24</v>
       </c>
       <c r="B135" t="n">
-        <v>46576</v>
+        <v>21494</v>
       </c>
       <c r="C135" t="n">
-        <v>101.46</v>
+        <v>39.19</v>
       </c>
       <c r="D135" t="n">
-        <v>23946</v>
+        <v>23902</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>93</v>
+        <v>51.34</v>
       </c>
       <c r="B136" t="n">
-        <v>28361</v>
+        <v>22142</v>
       </c>
       <c r="C136" t="n">
-        <v>90.76000000000001</v>
+        <v>46.94</v>
       </c>
       <c r="D136" t="n">
-        <v>25002</v>
+        <v>23838</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>91.41</v>
+        <v>51.4</v>
       </c>
       <c r="B137" t="n">
-        <v>29575</v>
+        <v>23178</v>
       </c>
       <c r="C137" t="n">
-        <v>94.54000000000001</v>
+        <v>54.52</v>
       </c>
       <c r="D137" t="n">
-        <v>25078</v>
+        <v>25094</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>103.72</v>
+        <v>51.45</v>
       </c>
       <c r="B138" t="n">
-        <v>47628</v>
+        <v>23650</v>
       </c>
       <c r="C138" t="n">
-        <v>99.45999999999999</v>
+        <v>38.7</v>
       </c>
       <c r="D138" t="n">
-        <v>23950</v>
+        <v>28428</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>99.13</v>
+        <v>51.68</v>
       </c>
       <c r="B139" t="n">
-        <v>45196</v>
+        <v>22440</v>
       </c>
       <c r="C139" t="n">
-        <v>101.15</v>
+        <v>61.77</v>
       </c>
       <c r="D139" t="n">
-        <v>23891</v>
+        <v>24052</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>91.66</v>
+        <v>51.71</v>
       </c>
       <c r="B140" t="n">
-        <v>27743</v>
+        <v>21512</v>
       </c>
       <c r="C140" t="n">
-        <v>94.41</v>
+        <v>45.66</v>
       </c>
       <c r="D140" t="n">
-        <v>23943</v>
+        <v>24015</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>101.25</v>
+        <v>52.4</v>
       </c>
       <c r="B141" t="n">
-        <v>46346</v>
+        <v>22166</v>
       </c>
       <c r="C141" t="n">
-        <v>101.57</v>
+        <v>57.44</v>
       </c>
       <c r="D141" t="n">
-        <v>28329</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>114.25</v>
+        <v>52.58</v>
       </c>
       <c r="B142" t="n">
-        <v>24420</v>
+        <v>20612</v>
       </c>
       <c r="C142" t="n">
-        <v>118.4</v>
+        <v>54.31</v>
       </c>
       <c r="D142" t="n">
-        <v>23940</v>
+        <v>23771</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>113.45</v>
+        <v>52.72</v>
       </c>
       <c r="B143" t="n">
-        <v>24690</v>
+        <v>22681</v>
       </c>
       <c r="C143" t="n">
-        <v>115.24</v>
+        <v>60.52</v>
       </c>
       <c r="D143" t="n">
-        <v>13.36</v>
+        <v>24902</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>101.54</v>
+        <v>52.99</v>
       </c>
       <c r="B144" t="n">
-        <v>46654</v>
+        <v>22671</v>
       </c>
       <c r="C144" t="n">
-        <v>97.38</v>
+        <v>41.33</v>
       </c>
       <c r="D144" t="n">
-        <v>28182</v>
+        <v>25063</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>21.92</v>
+        <v>53.02</v>
       </c>
       <c r="B145" t="n">
-        <v>22958</v>
+        <v>22625</v>
       </c>
       <c r="C145" t="n">
-        <v>22.33</v>
+        <v>61.1</v>
       </c>
       <c r="D145" t="n">
-        <v>24242</v>
+        <v>28082</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>93.73</v>
+        <v>53.33</v>
       </c>
       <c r="B146" t="n">
-        <v>30596</v>
+        <v>21472</v>
       </c>
       <c r="C146" t="n">
-        <v>94.92</v>
+        <v>61.76</v>
       </c>
       <c r="D146" t="n">
-        <v>24933</v>
+        <v>24866</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>90.48</v>
+        <v>54.18</v>
       </c>
       <c r="B147" t="n">
-        <v>27265</v>
+        <v>21515</v>
       </c>
       <c r="C147" t="n">
-        <v>92.65000000000001</v>
+        <v>59.51</v>
       </c>
       <c r="D147" t="n">
-        <v>13.36</v>
+        <v>25040</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>96.59999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="B148" t="n">
-        <v>41614</v>
+        <v>20331</v>
       </c>
       <c r="C148" t="n">
-        <v>98.37</v>
+        <v>52.91</v>
       </c>
       <c r="D148" t="n">
-        <v>23983</v>
+        <v>23947</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>102.01</v>
+        <v>54.8</v>
       </c>
       <c r="B149" t="n">
-        <v>46391</v>
+        <v>21090</v>
       </c>
       <c r="C149" t="n">
-        <v>97.66</v>
+        <v>57.27</v>
       </c>
       <c r="D149" t="n">
-        <v>24848</v>
+        <v>24221</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>104.4</v>
+        <v>56.26</v>
       </c>
       <c r="B150" t="n">
-        <v>49960</v>
+        <v>20008</v>
       </c>
       <c r="C150" t="n">
-        <v>104.9</v>
+        <v>61.7</v>
       </c>
       <c r="D150" t="n">
-        <v>28181</v>
+        <v>28139</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>104.91</v>
+        <v>56.62</v>
       </c>
       <c r="B151" t="n">
-        <v>48142</v>
+        <v>22071</v>
       </c>
       <c r="C151" t="n">
-        <v>103.46</v>
+        <v>48.93</v>
       </c>
       <c r="D151" t="n">
-        <v>28199</v>
+        <v>24895</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>24.12</v>
+        <v>56.76</v>
       </c>
       <c r="B152" t="n">
-        <v>23401</v>
+        <v>21706</v>
       </c>
       <c r="C152" t="n">
-        <v>22.93</v>
+        <v>48.84</v>
       </c>
       <c r="D152" t="n">
-        <v>28426</v>
+        <v>25124</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>100.55</v>
+        <v>56.92</v>
       </c>
       <c r="B153" t="n">
-        <v>47994</v>
+        <v>23451</v>
       </c>
       <c r="C153" t="n">
-        <v>101.96</v>
+        <v>56.13</v>
       </c>
       <c r="D153" t="n">
-        <v>28303</v>
+        <v>23943</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>95.04000000000001</v>
+        <v>57.31</v>
       </c>
       <c r="B154" t="n">
-        <v>34874</v>
+        <v>22619</v>
       </c>
       <c r="C154" t="n">
-        <v>94.13</v>
+        <v>60.57</v>
       </c>
       <c r="D154" t="n">
-        <v>23867</v>
+        <v>23843</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>107.6</v>
+        <v>57.5</v>
       </c>
       <c r="B155" t="n">
-        <v>42929</v>
+        <v>23798</v>
       </c>
       <c r="C155" t="n">
-        <v>108.37</v>
+        <v>55.22</v>
       </c>
       <c r="D155" t="n">
-        <v>23970</v>
+        <v>23941</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>110.35</v>
+        <v>58.42</v>
       </c>
       <c r="B156" t="n">
-        <v>31619</v>
+        <v>21261</v>
       </c>
       <c r="C156" t="n">
-        <v>106.42</v>
+        <v>68.17</v>
       </c>
       <c r="D156" t="n">
-        <v>23944</v>
+        <v>23865</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>114.29</v>
+        <v>59.89</v>
       </c>
       <c r="B157" t="n">
-        <v>25802</v>
+        <v>23869</v>
       </c>
       <c r="C157" t="n">
-        <v>117.71</v>
+        <v>68.42</v>
       </c>
       <c r="D157" t="n">
-        <v>24840</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2.92</v>
+        <v>59.99</v>
       </c>
       <c r="B158" t="n">
-        <v>26089</v>
+        <v>21306</v>
       </c>
       <c r="C158" t="n">
-        <v>3.37</v>
+        <v>63.5</v>
       </c>
       <c r="D158" t="n">
-        <v>24039</v>
+        <v>24838</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>111.73</v>
+        <v>60.23</v>
       </c>
       <c r="B159" t="n">
-        <v>32932</v>
+        <v>22639</v>
       </c>
       <c r="C159" t="n">
-        <v>112.35</v>
+        <v>56.15</v>
       </c>
       <c r="D159" t="n">
-        <v>28383</v>
+        <v>28422</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>113.45</v>
+        <v>60.27</v>
       </c>
       <c r="B160" t="n">
-        <v>26920</v>
+        <v>24237</v>
       </c>
       <c r="C160" t="n">
-        <v>112.43</v>
+        <v>51.74</v>
       </c>
       <c r="D160" t="n">
-        <v>28290</v>
+        <v>25163</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>112.73</v>
+        <v>60.59</v>
       </c>
       <c r="B161" t="n">
-        <v>27683</v>
+        <v>22168</v>
       </c>
       <c r="C161" t="n">
-        <v>115.23</v>
+        <v>55.22</v>
       </c>
       <c r="D161" t="n">
-        <v>25029</v>
+        <v>28227</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>113.07</v>
+        <v>60.78</v>
       </c>
       <c r="B162" t="n">
-        <v>27830</v>
+        <v>22583</v>
       </c>
       <c r="C162" t="n">
-        <v>114.89</v>
+        <v>50.05</v>
       </c>
       <c r="D162" t="n">
-        <v>13.36</v>
+        <v>28324</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>114.16</v>
+        <v>61</v>
       </c>
       <c r="B163" t="n">
-        <v>28003</v>
+        <v>20922</v>
       </c>
       <c r="C163" t="n">
-        <v>112.85</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D163" t="n">
-        <v>23801</v>
+        <v>23922</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>96.04000000000001</v>
+        <v>61.93</v>
       </c>
       <c r="B164" t="n">
-        <v>40220</v>
+        <v>21138</v>
       </c>
       <c r="C164" t="n">
-        <v>93.73</v>
+        <v>71.39</v>
       </c>
       <c r="D164" t="n">
-        <v>13.41</v>
+        <v>23772</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>96.90000000000001</v>
+        <v>62.18</v>
       </c>
       <c r="B165" t="n">
-        <v>40772</v>
+        <v>21497</v>
       </c>
       <c r="C165" t="n">
-        <v>96.34999999999999</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="D165" t="n">
-        <v>23917</v>
+        <v>23644</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>109.99</v>
+        <v>62.47</v>
       </c>
       <c r="B166" t="n">
-        <v>32419</v>
+        <v>23133</v>
       </c>
       <c r="C166" t="n">
-        <v>108.99</v>
+        <v>74.67</v>
       </c>
       <c r="D166" t="n">
-        <v>13.36</v>
+        <v>25197</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103.11</v>
+        <v>62.72</v>
       </c>
       <c r="B167" t="n">
-        <v>44994</v>
+        <v>22737</v>
       </c>
       <c r="C167" t="n">
-        <v>100.96</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="D167" t="n">
-        <v>13.41</v>
+        <v>23912</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>105.22</v>
+        <v>62.82</v>
       </c>
       <c r="B168" t="n">
-        <v>46703</v>
+        <v>22325</v>
       </c>
       <c r="C168" t="n">
-        <v>107.33</v>
+        <v>69.87</v>
       </c>
       <c r="D168" t="n">
-        <v>25077</v>
+        <v>23844</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>98.36</v>
+        <v>63.03</v>
       </c>
       <c r="B169" t="n">
-        <v>45399</v>
+        <v>21144</v>
       </c>
       <c r="C169" t="n">
-        <v>96.01000000000001</v>
+        <v>62.29</v>
       </c>
       <c r="D169" t="n">
-        <v>23750</v>
+        <v>23835</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>112.25</v>
+        <v>63.96</v>
       </c>
       <c r="B170" t="n">
-        <v>27089</v>
+        <v>23572</v>
       </c>
       <c r="C170" t="n">
-        <v>111.46</v>
+        <v>70.13</v>
       </c>
       <c r="D170" t="n">
-        <v>25072</v>
+        <v>28448</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>83.84</v>
+        <v>64.02</v>
       </c>
       <c r="B171" t="n">
-        <v>24082</v>
+        <v>21864</v>
       </c>
       <c r="C171" t="n">
-        <v>82.16</v>
+        <v>49.54</v>
       </c>
       <c r="D171" t="n">
-        <v>23790</v>
+        <v>25017</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>106.32</v>
+        <v>64.11</v>
       </c>
       <c r="B172" t="n">
-        <v>45192</v>
+        <v>23213</v>
       </c>
       <c r="C172" t="n">
-        <v>107.78</v>
+        <v>60.31</v>
       </c>
       <c r="D172" t="n">
-        <v>28386</v>
+        <v>24083</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>108.67</v>
+        <v>64.33</v>
       </c>
       <c r="B173" t="n">
-        <v>38628</v>
+        <v>23207</v>
       </c>
       <c r="C173" t="n">
-        <v>105.72</v>
+        <v>62.81</v>
       </c>
       <c r="D173" t="n">
-        <v>24890</v>
+        <v>23921</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>100.56</v>
+        <v>64.66</v>
       </c>
       <c r="B174" t="n">
-        <v>49066</v>
+        <v>23237</v>
       </c>
       <c r="C174" t="n">
-        <v>101.51</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="D174" t="n">
-        <v>23906</v>
+        <v>23742</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>109.47</v>
+        <v>64.7</v>
       </c>
       <c r="B175" t="n">
-        <v>37200</v>
+        <v>22465</v>
       </c>
       <c r="C175" t="n">
-        <v>107.66</v>
+        <v>59.91</v>
       </c>
       <c r="D175" t="n">
-        <v>28200</v>
+        <v>23960</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>99.05</v>
+        <v>65.02</v>
       </c>
       <c r="B176" t="n">
-        <v>46103</v>
+        <v>23368</v>
       </c>
       <c r="C176" t="n">
-        <v>102.26</v>
+        <v>72.42</v>
       </c>
       <c r="D176" t="n">
-        <v>24079</v>
+        <v>28195</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>105.87</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="B177" t="n">
-        <v>47831</v>
+        <v>21979</v>
       </c>
       <c r="C177" t="n">
-        <v>108.08</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="D177" t="n">
-        <v>25020</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>102.56</v>
+        <v>65.58</v>
       </c>
       <c r="B178" t="n">
-        <v>46397</v>
+        <v>21932</v>
       </c>
       <c r="C178" t="n">
-        <v>104.13</v>
+        <v>55.42</v>
       </c>
       <c r="D178" t="n">
-        <v>25032</v>
+        <v>24934</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122.33</v>
+        <v>66.2</v>
       </c>
       <c r="B179" t="n">
-        <v>25297</v>
+        <v>22848</v>
       </c>
       <c r="C179" t="n">
-        <v>119</v>
+        <v>46.41</v>
       </c>
       <c r="D179" t="n">
-        <v>24950</v>
+        <v>25063</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>92.77</v>
+        <v>66.75</v>
       </c>
       <c r="B180" t="n">
-        <v>29219</v>
+        <v>24445</v>
       </c>
       <c r="C180" t="n">
-        <v>96.81999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="D180" t="n">
-        <v>28333</v>
+        <v>24925</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>111.64</v>
+        <v>67.23</v>
       </c>
       <c r="B181" t="n">
-        <v>32169</v>
+        <v>22555</v>
       </c>
       <c r="C181" t="n">
-        <v>114.67</v>
+        <v>63.39</v>
       </c>
       <c r="D181" t="n">
-        <v>28389</v>
+        <v>28537</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>90.51000000000001</v>
+        <v>67.25</v>
       </c>
       <c r="B182" t="n">
-        <v>26962</v>
+        <v>22490</v>
       </c>
       <c r="C182" t="n">
-        <v>92.53</v>
+        <v>59.29</v>
       </c>
       <c r="D182" t="n">
-        <v>25080</v>
+        <v>23774</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>108.32</v>
+        <v>67.58</v>
       </c>
       <c r="B183" t="n">
-        <v>40589</v>
+        <v>22760</v>
       </c>
       <c r="C183" t="n">
-        <v>104.39</v>
+        <v>74.48</v>
       </c>
       <c r="D183" t="n">
-        <v>28158</v>
+        <v>25211</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>109.08</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="B184" t="n">
-        <v>38987</v>
+        <v>20664</v>
       </c>
       <c r="C184" t="n">
-        <v>110.61</v>
+        <v>60.29</v>
       </c>
       <c r="D184" t="n">
-        <v>25090</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>101.85</v>
+        <v>67.89</v>
       </c>
       <c r="B185" t="n">
-        <v>47727</v>
+        <v>21477</v>
       </c>
       <c r="C185" t="n">
-        <v>103.72</v>
+        <v>67.62</v>
       </c>
       <c r="D185" t="n">
-        <v>28351</v>
+        <v>28241</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>98.69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="B186" t="n">
-        <v>43916</v>
+        <v>23000</v>
       </c>
       <c r="C186" t="n">
-        <v>100.34</v>
+        <v>83.94</v>
       </c>
       <c r="D186" t="n">
-        <v>24907</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>114.76</v>
+        <v>68.47</v>
       </c>
       <c r="B187" t="n">
-        <v>24534</v>
+        <v>23839</v>
       </c>
       <c r="C187" t="n">
-        <v>113.41</v>
+        <v>59.11</v>
       </c>
       <c r="D187" t="n">
-        <v>13.76</v>
+        <v>25126</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>107.21</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="B188" t="n">
-        <v>47537</v>
+        <v>21460</v>
       </c>
       <c r="C188" t="n">
-        <v>106</v>
+        <v>56.69</v>
       </c>
       <c r="D188" t="n">
-        <v>23879</v>
+        <v>24870</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>114.77</v>
+        <v>68.73</v>
       </c>
       <c r="B189" t="n">
-        <v>25372</v>
+        <v>21687</v>
       </c>
       <c r="C189" t="n">
-        <v>112.9</v>
+        <v>78.97</v>
       </c>
       <c r="D189" t="n">
-        <v>23724</v>
+        <v>23916</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>107.1</v>
+        <v>68.98</v>
       </c>
       <c r="B190" t="n">
-        <v>44850</v>
+        <v>22947</v>
       </c>
       <c r="C190" t="n">
-        <v>109.43</v>
+        <v>75.2</v>
       </c>
       <c r="D190" t="n">
-        <v>28616</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>106.26</v>
+        <v>70.03</v>
       </c>
       <c r="B191" t="n">
-        <v>49080</v>
+        <v>22520</v>
       </c>
       <c r="C191" t="n">
-        <v>102.98</v>
+        <v>49.49</v>
       </c>
       <c r="D191" t="n">
-        <v>28001</v>
+        <v>23745</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>102.98</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="B192" t="n">
-        <v>48690</v>
+        <v>21165</v>
       </c>
       <c r="C192" t="n">
-        <v>101.06</v>
+        <v>74.06</v>
       </c>
       <c r="D192" t="n">
-        <v>25035</v>
+        <v>24076</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>91.68000000000001</v>
+        <v>70.33</v>
       </c>
       <c r="B193" t="n">
-        <v>29177</v>
+        <v>21772</v>
       </c>
       <c r="C193" t="n">
-        <v>91.20999999999999</v>
+        <v>76</v>
       </c>
       <c r="D193" t="n">
-        <v>28268</v>
+        <v>24968</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>99.48</v>
+        <v>70.44</v>
       </c>
       <c r="B194" t="n">
-        <v>45343</v>
+        <v>21231</v>
       </c>
       <c r="C194" t="n">
-        <v>96.06</v>
+        <v>62.65</v>
       </c>
       <c r="D194" t="n">
-        <v>23778</v>
+        <v>23937</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>99.84999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="B195" t="n">
-        <v>46216</v>
+        <v>22041</v>
       </c>
       <c r="C195" t="n">
-        <v>101.01</v>
+        <v>83.38</v>
       </c>
       <c r="D195" t="n">
-        <v>23878</v>
+        <v>28192</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>106.76</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="B196" t="n">
-        <v>42368</v>
+        <v>23123</v>
       </c>
       <c r="C196" t="n">
-        <v>102.26</v>
+        <v>64.06</v>
       </c>
       <c r="D196" t="n">
-        <v>23844</v>
+        <v>24955</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>92.8</v>
+        <v>70.97</v>
       </c>
       <c r="B197" t="n">
-        <v>27033</v>
+        <v>21723</v>
       </c>
       <c r="C197" t="n">
-        <v>94.68000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="D197" t="n">
-        <v>24085</v>
+        <v>28389</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133.09</v>
+        <v>71.23</v>
       </c>
       <c r="B198" t="n">
-        <v>23321</v>
+        <v>22248</v>
       </c>
       <c r="C198" t="n">
-        <v>133.42</v>
+        <v>66.48</v>
       </c>
       <c r="D198" t="n">
-        <v>13.41</v>
+        <v>23983</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>93.11</v>
+        <v>71.91</v>
       </c>
       <c r="B199" t="n">
-        <v>29660</v>
+        <v>23035</v>
       </c>
       <c r="C199" t="n">
-        <v>95.63</v>
+        <v>85.36</v>
       </c>
       <c r="D199" t="n">
-        <v>23951</v>
+        <v>23862</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>100.74</v>
+        <v>72.09</v>
       </c>
       <c r="B200" t="n">
-        <v>49062</v>
+        <v>22265</v>
       </c>
       <c r="C200" t="n">
-        <v>98.58</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="D200" t="n">
-        <v>28303</v>
+        <v>28175</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>109.95</v>
+        <v>72.41</v>
       </c>
       <c r="B201" t="n">
-        <v>31900</v>
+        <v>22729</v>
       </c>
       <c r="C201" t="n">
-        <v>109.47</v>
+        <v>69.22</v>
       </c>
       <c r="D201" t="n">
-        <v>13.36</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>78.88</v>
+        <v>73.14</v>
       </c>
       <c r="B202" t="n">
-        <v>24407</v>
+        <v>22797</v>
       </c>
       <c r="C202" t="n">
-        <v>80.56</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="D202" t="n">
-        <v>25013</v>
+        <v>28268</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>107.57</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="B203" t="n">
-        <v>43192</v>
+        <v>21578</v>
       </c>
       <c r="C203" t="n">
-        <v>109.06</v>
+        <v>75.31</v>
       </c>
       <c r="D203" t="n">
-        <v>24921</v>
+        <v>23778</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>93.44</v>
+        <v>73.61</v>
       </c>
       <c r="B204" t="n">
-        <v>30164</v>
+        <v>21442</v>
       </c>
       <c r="C204" t="n">
-        <v>92.33</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="D204" t="n">
-        <v>25098</v>
+        <v>24965</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113.34</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="B205" t="n">
-        <v>24957</v>
+        <v>21280</v>
       </c>
       <c r="C205" t="n">
-        <v>109.54</v>
+        <v>79.34</v>
       </c>
       <c r="D205" t="n">
-        <v>25096</v>
+        <v>23938</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>104.12</v>
+        <v>74.11</v>
       </c>
       <c r="B206" t="n">
-        <v>47784</v>
+        <v>21701</v>
       </c>
       <c r="C206" t="n">
-        <v>102.67</v>
+        <v>70.45</v>
       </c>
       <c r="D206" t="n">
-        <v>13.41</v>
+        <v>23860</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>110.52</v>
+        <v>74.44</v>
       </c>
       <c r="B207" t="n">
-        <v>32618</v>
+        <v>21452</v>
       </c>
       <c r="C207" t="n">
-        <v>108.02</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="D207" t="n">
-        <v>25039</v>
+        <v>25105</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>92.8</v>
+        <v>74.58</v>
       </c>
       <c r="B208" t="n">
-        <v>30637</v>
+        <v>21768</v>
       </c>
       <c r="C208" t="n">
-        <v>93.52</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="D208" t="n">
-        <v>23930</v>
+        <v>28403</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>24.56</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="B209" t="n">
-        <v>26948</v>
+        <v>21445</v>
       </c>
       <c r="C209" t="n">
-        <v>23.77</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="D209" t="n">
-        <v>28299</v>
+        <v>28301</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>91.95</v>
+        <v>74.77</v>
       </c>
       <c r="B210" t="n">
-        <v>28063</v>
+        <v>20711</v>
       </c>
       <c r="C210" t="n">
-        <v>90.77</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="D210" t="n">
-        <v>25199</v>
+        <v>23878</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>90.95999999999999</v>
+        <v>74.78</v>
       </c>
       <c r="B211" t="n">
-        <v>27603</v>
+        <v>23320</v>
       </c>
       <c r="C211" t="n">
-        <v>94.16</v>
+        <v>67.88</v>
       </c>
       <c r="D211" t="n">
-        <v>24945</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>106.29</v>
+        <v>75.28</v>
       </c>
       <c r="B212" t="n">
-        <v>43187</v>
+        <v>22685</v>
       </c>
       <c r="C212" t="n">
-        <v>107.42</v>
+        <v>85.27</v>
       </c>
       <c r="D212" t="n">
-        <v>23750</v>
+        <v>23780</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>111.58</v>
+        <v>75.42</v>
       </c>
       <c r="B213" t="n">
-        <v>30993</v>
+        <v>22464</v>
       </c>
       <c r="C213" t="n">
-        <v>114.33</v>
+        <v>71.67</v>
       </c>
       <c r="D213" t="n">
-        <v>23877</v>
+        <v>28381</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>113.45</v>
+        <v>75.47</v>
       </c>
       <c r="B214" t="n">
-        <v>26130</v>
+        <v>22973</v>
       </c>
       <c r="C214" t="n">
-        <v>114.14</v>
+        <v>84.73</v>
       </c>
       <c r="D214" t="n">
-        <v>23848</v>
+        <v>23920</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>114.87</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="B215" t="n">
-        <v>25065</v>
+        <v>21890</v>
       </c>
       <c r="C215" t="n">
-        <v>112.91</v>
+        <v>72.33</v>
       </c>
       <c r="D215" t="n">
-        <v>28287</v>
+        <v>24063</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>92.81</v>
+        <v>75.56</v>
       </c>
       <c r="B216" t="n">
-        <v>29430</v>
+        <v>21754</v>
       </c>
       <c r="C216" t="n">
-        <v>91.81</v>
+        <v>91.11</v>
       </c>
       <c r="D216" t="n">
-        <v>23842</v>
+        <v>24028</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>93.76000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="B217" t="n">
-        <v>31458</v>
+        <v>21752</v>
       </c>
       <c r="C217" t="n">
-        <v>94.43000000000001</v>
+        <v>68.81</v>
       </c>
       <c r="D217" t="n">
-        <v>24054</v>
+        <v>28196</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>96.54000000000001</v>
+        <v>75.97</v>
       </c>
       <c r="B218" t="n">
-        <v>37645</v>
+        <v>22388</v>
       </c>
       <c r="C218" t="n">
-        <v>94.77</v>
+        <v>82.97</v>
       </c>
       <c r="D218" t="n">
-        <v>23907</v>
+        <v>23830</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>90.05</v>
+        <v>76</v>
       </c>
       <c r="B219" t="n">
-        <v>24621</v>
+        <v>21351</v>
       </c>
       <c r="C219" t="n">
-        <v>93.20999999999999</v>
+        <v>78.66</v>
       </c>
       <c r="D219" t="n">
-        <v>28233</v>
+        <v>28290</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>103.64</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="B220" t="n">
-        <v>51687</v>
+        <v>22240</v>
       </c>
       <c r="C220" t="n">
-        <v>100.01</v>
+        <v>80.03</v>
       </c>
       <c r="D220" t="n">
-        <v>28322</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>94.58</v>
+        <v>76.8</v>
       </c>
       <c r="B221" t="n">
-        <v>33083</v>
+        <v>20978</v>
       </c>
       <c r="C221" t="n">
-        <v>98.52</v>
+        <v>61.19</v>
       </c>
       <c r="D221" t="n">
-        <v>28153</v>
+        <v>23885</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>99.64</v>
+        <v>76.87</v>
       </c>
       <c r="B222" t="n">
-        <v>46407</v>
+        <v>21590</v>
       </c>
       <c r="C222" t="n">
-        <v>99.83</v>
+        <v>59.99</v>
       </c>
       <c r="D222" t="n">
-        <v>23909</v>
+        <v>24083</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>104.15</v>
+        <v>77.05</v>
       </c>
       <c r="B223" t="n">
-        <v>50982</v>
+        <v>20796</v>
       </c>
       <c r="C223" t="n">
-        <v>101.41</v>
+        <v>89.06</v>
       </c>
       <c r="D223" t="n">
-        <v>28092</v>
+        <v>28326</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>100.99</v>
+        <v>77.37</v>
       </c>
       <c r="B224" t="n">
-        <v>51285</v>
+        <v>21646</v>
       </c>
       <c r="C224" t="n">
-        <v>101.67</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="D224" t="n">
-        <v>28480</v>
+        <v>24903</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>112.22</v>
+        <v>77.8</v>
       </c>
       <c r="B225" t="n">
-        <v>31424</v>
+        <v>21501</v>
       </c>
       <c r="C225" t="n">
-        <v>108.78</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D225" t="n">
-        <v>28189</v>
+        <v>28090</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>111.5</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="B226" t="n">
-        <v>30277</v>
+        <v>21373</v>
       </c>
       <c r="C226" t="n">
-        <v>115.91</v>
+        <v>71.5</v>
       </c>
       <c r="D226" t="n">
-        <v>23903</v>
+        <v>24983</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>112.04</v>
+        <v>78.19</v>
       </c>
       <c r="B227" t="n">
-        <v>32577</v>
+        <v>21460</v>
       </c>
       <c r="C227" t="n">
-        <v>116.27</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D227" t="n">
-        <v>28426</v>
+        <v>28252</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>99.31999999999999</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="B228" t="n">
-        <v>46270</v>
+        <v>21445</v>
       </c>
       <c r="C228" t="n">
-        <v>94.70999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="D228" t="n">
-        <v>28245</v>
+        <v>28276</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>90.59</v>
+        <v>79.06</v>
       </c>
       <c r="B229" t="n">
-        <v>25734</v>
+        <v>21377</v>
       </c>
       <c r="C229" t="n">
-        <v>90.59</v>
+        <v>91.89</v>
       </c>
       <c r="D229" t="n">
-        <v>23936</v>
+        <v>24975</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>100.37</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="B230" t="n">
-        <v>44311</v>
+        <v>22385</v>
       </c>
       <c r="C230" t="n">
-        <v>102.21</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="D230" t="n">
-        <v>28367</v>
+        <v>24856</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>112.22</v>
+        <v>79.98</v>
       </c>
       <c r="B231" t="n">
-        <v>30043</v>
+        <v>20034</v>
       </c>
       <c r="C231" t="n">
-        <v>115.72</v>
+        <v>88.78</v>
       </c>
       <c r="D231" t="n">
-        <v>28211</v>
+        <v>28265</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>73.14</v>
+        <v>80</v>
       </c>
       <c r="B232" t="n">
-        <v>25357</v>
+        <v>22346</v>
       </c>
       <c r="C232" t="n">
-        <v>74.38</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="D232" t="n">
-        <v>24074</v>
+        <v>24029</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>101.43</v>
+        <v>80.34</v>
       </c>
       <c r="B233" t="n">
-        <v>46823</v>
+        <v>22028</v>
       </c>
       <c r="C233" t="n">
-        <v>103.1</v>
+        <v>76.86</v>
       </c>
       <c r="D233" t="n">
-        <v>23765</v>
+        <v>23899</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>85.69</v>
+        <v>81.12</v>
       </c>
       <c r="B234" t="n">
-        <v>25868</v>
+        <v>22104</v>
       </c>
       <c r="C234" t="n">
-        <v>88.31999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="D234" t="n">
-        <v>23966</v>
+        <v>25005</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>111.89</v>
+        <v>81.14</v>
       </c>
       <c r="B235" t="n">
-        <v>28525</v>
+        <v>21501</v>
       </c>
       <c r="C235" t="n">
-        <v>111.48</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="D235" t="n">
-        <v>25154</v>
+        <v>23927</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>95.36</v>
+        <v>81.94</v>
       </c>
       <c r="B236" t="n">
-        <v>37098</v>
+        <v>22214</v>
       </c>
       <c r="C236" t="n">
-        <v>92.93000000000001</v>
+        <v>85.11</v>
       </c>
       <c r="D236" t="n">
-        <v>24938</v>
+        <v>25237</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>4.61</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="B237" t="n">
-        <v>24884</v>
+        <v>22880</v>
       </c>
       <c r="C237" t="n">
-        <v>4.83</v>
+        <v>102.6</v>
       </c>
       <c r="D237" t="n">
-        <v>13.24</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>22.83</v>
+        <v>82.62</v>
       </c>
       <c r="B238" t="n">
-        <v>24718</v>
+        <v>21439</v>
       </c>
       <c r="C238" t="n">
-        <v>23.19</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="D238" t="n">
-        <v>24929</v>
+        <v>24021</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>103.7</v>
+        <v>83.38</v>
       </c>
       <c r="B239" t="n">
-        <v>50635</v>
+        <v>20796</v>
       </c>
       <c r="C239" t="n">
-        <v>107.35</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="D239" t="n">
-        <v>28280</v>
+        <v>28179</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>100.54</v>
+        <v>83.56</v>
       </c>
       <c r="B240" t="n">
-        <v>48136</v>
+        <v>21058</v>
       </c>
       <c r="C240" t="n">
-        <v>102.62</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D240" t="n">
-        <v>23958</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>21.84</v>
+        <v>83.81</v>
       </c>
       <c r="B241" t="n">
-        <v>28958</v>
+        <v>21643</v>
       </c>
       <c r="C241" t="n">
-        <v>21.59</v>
+        <v>91.89</v>
       </c>
       <c r="D241" t="n">
-        <v>24842</v>
+        <v>23849</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>114.1</v>
+        <v>83.83</v>
       </c>
       <c r="B242" t="n">
-        <v>27829</v>
+        <v>21046</v>
       </c>
       <c r="C242" t="n">
-        <v>110.26</v>
+        <v>67.77</v>
       </c>
       <c r="D242" t="n">
-        <v>23789</v>
+        <v>24958</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>143.1</v>
+        <v>83.88</v>
       </c>
       <c r="B243" t="n">
-        <v>25925</v>
+        <v>21545</v>
       </c>
       <c r="C243" t="n">
-        <v>144.55</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="D243" t="n">
-        <v>23954</v>
+        <v>28183</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>114.38</v>
+        <v>84.2</v>
       </c>
       <c r="B244" t="n">
-        <v>25667</v>
+        <v>20638</v>
       </c>
       <c r="C244" t="n">
-        <v>118.93</v>
+        <v>83.61</v>
       </c>
       <c r="D244" t="n">
-        <v>25063</v>
+        <v>28355</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>91.83</v>
+        <v>84.95</v>
       </c>
       <c r="B245" t="n">
-        <v>30987</v>
+        <v>21257</v>
       </c>
       <c r="C245" t="n">
-        <v>91.45</v>
+        <v>100.42</v>
       </c>
       <c r="D245" t="n">
-        <v>25086</v>
+        <v>23936</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>102.16</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="B246" t="n">
-        <v>48379</v>
+        <v>21830</v>
       </c>
       <c r="C246" t="n">
-        <v>104.6</v>
+        <v>81.03</v>
       </c>
       <c r="D246" t="n">
-        <v>23802</v>
+        <v>28421</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>28.98</v>
+        <v>85.16</v>
       </c>
       <c r="B247" t="n">
-        <v>27535</v>
+        <v>21575</v>
       </c>
       <c r="C247" t="n">
-        <v>27.56</v>
+        <v>77.53</v>
       </c>
       <c r="D247" t="n">
-        <v>23937</v>
+        <v>24793</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>97.95999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="B248" t="n">
-        <v>41666</v>
+        <v>21845</v>
       </c>
       <c r="C248" t="n">
-        <v>98.81999999999999</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>25081</v>
+        <v>25020</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>110.45</v>
+        <v>86.25</v>
       </c>
       <c r="B249" t="n">
-        <v>31997</v>
+        <v>22425</v>
       </c>
       <c r="C249" t="n">
-        <v>110.29</v>
+        <v>79.61</v>
       </c>
       <c r="D249" t="n">
-        <v>28261</v>
+        <v>24142</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>112.04</v>
+        <v>86.44</v>
       </c>
       <c r="B250" t="n">
-        <v>28309</v>
+        <v>22252</v>
       </c>
       <c r="C250" t="n">
-        <v>114.07</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="D250" t="n">
-        <v>25000</v>
+        <v>23929</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>108.55</v>
+        <v>87.47</v>
       </c>
       <c r="B251" t="n">
-        <v>37220</v>
+        <v>20644</v>
       </c>
       <c r="C251" t="n">
-        <v>111.62</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="D251" t="n">
-        <v>28406</v>
+        <v>23916</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>100.15</v>
+        <v>87.5</v>
       </c>
       <c r="B252" t="n">
-        <v>49127</v>
+        <v>20833</v>
       </c>
       <c r="C252" t="n">
-        <v>102.61</v>
+        <v>100.78</v>
       </c>
       <c r="D252" t="n">
-        <v>24087</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>65.27</v>
+        <v>88.27</v>
       </c>
       <c r="B253" t="n">
-        <v>25839</v>
+        <v>22104</v>
       </c>
       <c r="C253" t="n">
-        <v>64.86</v>
+        <v>97.38</v>
       </c>
       <c r="D253" t="n">
-        <v>28098</v>
+        <v>23860</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>92.94</v>
+        <v>89.69</v>
       </c>
       <c r="B254" t="n">
-        <v>30376</v>
+        <v>22053</v>
       </c>
       <c r="C254" t="n">
-        <v>96.12</v>
+        <v>93.13</v>
       </c>
       <c r="D254" t="n">
-        <v>28283</v>
+        <v>25052</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>103.58</v>
+        <v>90.23</v>
       </c>
       <c r="B255" t="n">
-        <v>48140</v>
+        <v>20996</v>
       </c>
       <c r="C255" t="n">
-        <v>105.8</v>
+        <v>65.69</v>
       </c>
       <c r="D255" t="n">
-        <v>28325</v>
+        <v>23826</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>113.01</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="B256" t="n">
-        <v>27567</v>
+        <v>22575</v>
       </c>
       <c r="C256" t="n">
-        <v>108.89</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="D256" t="n">
-        <v>24998</v>
+        <v>28358</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>98.3</v>
+        <v>91.02</v>
       </c>
       <c r="B257" t="n">
-        <v>42805</v>
+        <v>21540</v>
       </c>
       <c r="C257" t="n">
-        <v>95.06999999999999</v>
+        <v>89.13</v>
       </c>
       <c r="D257" t="n">
-        <v>24752</v>
+        <v>23874</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>102.98</v>
+        <v>91.09</v>
       </c>
       <c r="B258" t="n">
-        <v>49944</v>
+        <v>22912</v>
       </c>
       <c r="C258" t="n">
-        <v>100.79</v>
+        <v>99.09</v>
       </c>
       <c r="D258" t="n">
-        <v>28254</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>64.98999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="B259" t="n">
-        <v>26454</v>
+        <v>22793</v>
       </c>
       <c r="C259" t="n">
-        <v>65.31999999999999</v>
+        <v>89.87</v>
       </c>
       <c r="D259" t="n">
-        <v>23875</v>
+        <v>24087</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>101.43</v>
+        <v>91.8</v>
       </c>
       <c r="B260" t="n">
-        <v>46887</v>
+        <v>23277</v>
       </c>
       <c r="C260" t="n">
-        <v>102.97</v>
+        <v>73.63</v>
       </c>
       <c r="D260" t="n">
-        <v>23892</v>
+        <v>25026</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>90.81999999999999</v>
+        <v>91.88</v>
       </c>
       <c r="B261" t="n">
-        <v>28857</v>
+        <v>22381</v>
       </c>
       <c r="C261" t="n">
-        <v>90.72</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>23906</v>
+        <v>25043</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>113.46</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="B262" t="n">
-        <v>27440</v>
+        <v>23916</v>
       </c>
       <c r="C262" t="n">
-        <v>110.37</v>
+        <v>84.58</v>
       </c>
       <c r="D262" t="n">
-        <v>28282</v>
+        <v>28374</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>90.73999999999999</v>
+        <v>92.14</v>
       </c>
       <c r="B263" t="n">
-        <v>26724</v>
+        <v>23122</v>
       </c>
       <c r="C263" t="n">
-        <v>91.28</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="D263" t="n">
-        <v>24853</v>
+        <v>28190</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>92.98999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="B264" t="n">
-        <v>33981</v>
+        <v>23258</v>
       </c>
       <c r="C264" t="n">
-        <v>90.62</v>
+        <v>102.58</v>
       </c>
       <c r="D264" t="n">
-        <v>24860</v>
+        <v>23846</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>110.78</v>
+        <v>92.63</v>
       </c>
       <c r="B265" t="n">
-        <v>32690</v>
+        <v>23138</v>
       </c>
       <c r="C265" t="n">
-        <v>108.31</v>
+        <v>108.4</v>
       </c>
       <c r="D265" t="n">
-        <v>23967</v>
+        <v>25095</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>94.95</v>
+        <v>92.87</v>
       </c>
       <c r="B266" t="n">
-        <v>34087</v>
+        <v>22930</v>
       </c>
       <c r="C266" t="n">
-        <v>92.33</v>
+        <v>86.67</v>
       </c>
       <c r="D266" t="n">
-        <v>28089</v>
+        <v>24031</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>95.59999999999999</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="B267" t="n">
-        <v>36915</v>
+        <v>25092</v>
       </c>
       <c r="C267" t="n">
-        <v>96.15000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="D267" t="n">
-        <v>25011</v>
+        <v>28268</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>51.62</v>
+        <v>93.83</v>
       </c>
       <c r="B268" t="n">
-        <v>25857</v>
+        <v>24784</v>
       </c>
       <c r="C268" t="n">
-        <v>54.54</v>
+        <v>79.89</v>
       </c>
       <c r="D268" t="n">
-        <v>28206</v>
+        <v>23840</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>114.27</v>
+        <v>94.69</v>
       </c>
       <c r="B269" t="n">
-        <v>27998</v>
+        <v>25358</v>
       </c>
       <c r="C269" t="n">
-        <v>111.06</v>
+        <v>109.29</v>
       </c>
       <c r="D269" t="n">
-        <v>24913</v>
+        <v>28381</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>91.62</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="B270" t="n">
-        <v>28637</v>
+        <v>25745</v>
       </c>
       <c r="C270" t="n">
-        <v>89.95</v>
+        <v>72.72</v>
       </c>
       <c r="D270" t="n">
-        <v>23832</v>
+        <v>24035</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>97.45999999999999</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="B271" t="n">
-        <v>42770</v>
+        <v>26894</v>
       </c>
       <c r="C271" t="n">
-        <v>95.66</v>
+        <v>90.25</v>
       </c>
       <c r="D271" t="n">
-        <v>13.76</v>
+        <v>24888</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>97.77</v>
+        <v>96.13</v>
       </c>
       <c r="B272" t="n">
-        <v>42422</v>
+        <v>28330</v>
       </c>
       <c r="C272" t="n">
-        <v>97.70999999999999</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="D272" t="n">
-        <v>23950</v>
+        <v>24997</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>108.71</v>
+        <v>96.62</v>
       </c>
       <c r="B273" t="n">
-        <v>34496</v>
+        <v>29198</v>
       </c>
       <c r="C273" t="n">
-        <v>105.86</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="D273" t="n">
-        <v>13.98</v>
+        <v>28399</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>103.08</v>
+        <v>98.66</v>
       </c>
       <c r="B274" t="n">
-        <v>50129</v>
+        <v>33612</v>
       </c>
       <c r="C274" t="n">
-        <v>106.14</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="D274" t="n">
-        <v>24964</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>95.06</v>
+        <v>98.94</v>
       </c>
       <c r="B275" t="n">
-        <v>33180</v>
+        <v>34043</v>
       </c>
       <c r="C275" t="n">
-        <v>95.14</v>
+        <v>109.92</v>
       </c>
       <c r="D275" t="n">
         <v>13.24</v>
@@ -4288,2197 +4288,2197 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>100.69</v>
+        <v>99.12</v>
       </c>
       <c r="B276" t="n">
-        <v>48396</v>
+        <v>34788</v>
       </c>
       <c r="C276" t="n">
-        <v>101.83</v>
+        <v>101.51</v>
       </c>
       <c r="D276" t="n">
-        <v>25005</v>
+        <v>23902</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>114.23</v>
+        <v>99.52</v>
       </c>
       <c r="B277" t="n">
-        <v>27763</v>
+        <v>34573</v>
       </c>
       <c r="C277" t="n">
-        <v>112.38</v>
+        <v>101.66</v>
       </c>
       <c r="D277" t="n">
-        <v>24033</v>
+        <v>23942</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>172.09</v>
+        <v>101.03</v>
       </c>
       <c r="B278" t="n">
-        <v>25447</v>
+        <v>38521</v>
       </c>
       <c r="C278" t="n">
-        <v>177.05</v>
+        <v>116.84</v>
       </c>
       <c r="D278" t="n">
-        <v>28291</v>
+        <v>25137</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>114.54</v>
+        <v>101.58</v>
       </c>
       <c r="B279" t="n">
-        <v>24169</v>
+        <v>37609</v>
       </c>
       <c r="C279" t="n">
-        <v>117.88</v>
+        <v>89.28</v>
       </c>
       <c r="D279" t="n">
-        <v>23879</v>
+        <v>24072</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>103.35</v>
+        <v>101.81</v>
       </c>
       <c r="B280" t="n">
-        <v>47399</v>
+        <v>39085</v>
       </c>
       <c r="C280" t="n">
-        <v>104.14</v>
+        <v>96.28</v>
       </c>
       <c r="D280" t="n">
-        <v>25032</v>
+        <v>28353</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>90.48</v>
+        <v>102.63</v>
       </c>
       <c r="B281" t="n">
-        <v>25825</v>
+        <v>39778</v>
       </c>
       <c r="C281" t="n">
-        <v>87.42</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="D281" t="n">
-        <v>25035</v>
+        <v>24883</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>105.94</v>
+        <v>102.87</v>
       </c>
       <c r="B282" t="n">
-        <v>48318</v>
+        <v>39701</v>
       </c>
       <c r="C282" t="n">
-        <v>105.5</v>
+        <v>124.03</v>
       </c>
       <c r="D282" t="n">
-        <v>25043</v>
+        <v>24049</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>91.62</v>
+        <v>103.14</v>
       </c>
       <c r="B283" t="n">
-        <v>27166</v>
+        <v>37076</v>
       </c>
       <c r="C283" t="n">
-        <v>94.51000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="D283" t="n">
-        <v>24027</v>
+        <v>24730</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>105.08</v>
+        <v>103.33</v>
       </c>
       <c r="B284" t="n">
-        <v>46514</v>
+        <v>38893</v>
       </c>
       <c r="C284" t="n">
-        <v>105.79</v>
+        <v>108.19</v>
       </c>
       <c r="D284" t="n">
-        <v>23957</v>
+        <v>28320</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>115.41</v>
+        <v>103.83</v>
       </c>
       <c r="B285" t="n">
-        <v>27430</v>
+        <v>37857</v>
       </c>
       <c r="C285" t="n">
-        <v>115.36</v>
+        <v>98.95</v>
       </c>
       <c r="D285" t="n">
-        <v>28368</v>
+        <v>23940</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1</v>
+        <v>104.49</v>
       </c>
       <c r="B286" t="n">
-        <v>27017</v>
+        <v>38313</v>
       </c>
       <c r="C286" t="n">
-        <v>0.88</v>
+        <v>101.5</v>
       </c>
       <c r="D286" t="n">
-        <v>24966</v>
+        <v>23896</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>111.13</v>
+        <v>104.98</v>
       </c>
       <c r="B287" t="n">
-        <v>34606</v>
+        <v>37621</v>
       </c>
       <c r="C287" t="n">
-        <v>108.33</v>
+        <v>110.79</v>
       </c>
       <c r="D287" t="n">
-        <v>13.41</v>
+        <v>25031</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>100.31</v>
+        <v>105.16</v>
       </c>
       <c r="B288" t="n">
-        <v>48565</v>
+        <v>37101</v>
       </c>
       <c r="C288" t="n">
-        <v>104.33</v>
+        <v>118.62</v>
       </c>
       <c r="D288" t="n">
-        <v>24957</v>
+        <v>25010</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>107.27</v>
+        <v>105.94</v>
       </c>
       <c r="B289" t="n">
-        <v>42321</v>
+        <v>35462</v>
       </c>
       <c r="C289" t="n">
-        <v>111.04</v>
+        <v>106.89</v>
       </c>
       <c r="D289" t="n">
-        <v>28357</v>
+        <v>23839</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>65.84</v>
+        <v>106.23</v>
       </c>
       <c r="B290" t="n">
-        <v>27404</v>
+        <v>34913</v>
       </c>
       <c r="C290" t="n">
-        <v>65.77</v>
+        <v>112.76</v>
       </c>
       <c r="D290" t="n">
-        <v>24994</v>
+        <v>23895</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>98.37</v>
+        <v>106.53</v>
       </c>
       <c r="B291" t="n">
-        <v>43958</v>
+        <v>34627</v>
       </c>
       <c r="C291" t="n">
-        <v>97.5</v>
+        <v>109.23</v>
       </c>
       <c r="D291" t="n">
-        <v>13.41</v>
+        <v>23803</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>100.09</v>
+        <v>106.65</v>
       </c>
       <c r="B292" t="n">
-        <v>47552</v>
+        <v>33687</v>
       </c>
       <c r="C292" t="n">
-        <v>102.2</v>
+        <v>104.28</v>
       </c>
       <c r="D292" t="n">
-        <v>28279</v>
+        <v>23896</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>113.77</v>
+        <v>106.94</v>
       </c>
       <c r="B293" t="n">
-        <v>24334</v>
+        <v>33247</v>
       </c>
       <c r="C293" t="n">
-        <v>113.1</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="D293" t="n">
-        <v>25072</v>
+        <v>24994</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>108.44</v>
+        <v>107.64</v>
       </c>
       <c r="B294" t="n">
-        <v>37154</v>
+        <v>32422</v>
       </c>
       <c r="C294" t="n">
-        <v>103.73</v>
+        <v>120.45</v>
       </c>
       <c r="D294" t="n">
-        <v>25000</v>
+        <v>28239</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>99.84999999999999</v>
+        <v>107.72</v>
       </c>
       <c r="B295" t="n">
-        <v>47355</v>
+        <v>32205</v>
       </c>
       <c r="C295" t="n">
-        <v>97</v>
+        <v>125.67</v>
       </c>
       <c r="D295" t="n">
-        <v>24973</v>
+        <v>28224</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>93.91</v>
+        <v>107.82</v>
       </c>
       <c r="B296" t="n">
-        <v>31263</v>
+        <v>32242</v>
       </c>
       <c r="C296" t="n">
-        <v>95.51000000000001</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="D296" t="n">
-        <v>23849</v>
+        <v>23908</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>103.84</v>
+        <v>107.98</v>
       </c>
       <c r="B297" t="n">
-        <v>48611</v>
+        <v>31029</v>
       </c>
       <c r="C297" t="n">
-        <v>100.05</v>
+        <v>105.34</v>
       </c>
       <c r="D297" t="n">
-        <v>24991</v>
+        <v>23940</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>96.26000000000001</v>
+        <v>108.99</v>
       </c>
       <c r="B298" t="n">
-        <v>37391</v>
+        <v>28823</v>
       </c>
       <c r="C298" t="n">
-        <v>94.64</v>
+        <v>123.01</v>
       </c>
       <c r="D298" t="n">
-        <v>25066</v>
+        <v>23941</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>104.94</v>
+        <v>109.02</v>
       </c>
       <c r="B299" t="n">
-        <v>48974</v>
+        <v>28868</v>
       </c>
       <c r="C299" t="n">
-        <v>104.21</v>
+        <v>127.36</v>
       </c>
       <c r="D299" t="n">
-        <v>28198</v>
+        <v>23825</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>23.4</v>
+        <v>109.09</v>
       </c>
       <c r="B300" t="n">
-        <v>24554</v>
+        <v>28292</v>
       </c>
       <c r="C300" t="n">
-        <v>23.52</v>
+        <v>103.3</v>
       </c>
       <c r="D300" t="n">
-        <v>28088</v>
+        <v>25120</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>102.45</v>
+        <v>109.21</v>
       </c>
       <c r="B301" t="n">
-        <v>49705</v>
+        <v>28729</v>
       </c>
       <c r="C301" t="n">
-        <v>105.21</v>
+        <v>119.74</v>
       </c>
       <c r="D301" t="n">
-        <v>25195</v>
+        <v>23920</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>90.51000000000001</v>
+        <v>109.7</v>
       </c>
       <c r="B302" t="n">
-        <v>25946</v>
+        <v>27848</v>
       </c>
       <c r="C302" t="n">
-        <v>90.27</v>
+        <v>133.57</v>
       </c>
       <c r="D302" t="n">
-        <v>23856</v>
+        <v>23832</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>98.15000000000001</v>
+        <v>110.23</v>
       </c>
       <c r="B303" t="n">
-        <v>42702</v>
+        <v>26073</v>
       </c>
       <c r="C303" t="n">
-        <v>94.40000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="D303" t="n">
-        <v>24995</v>
+        <v>24864</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>113.36</v>
+        <v>110.31</v>
       </c>
       <c r="B304" t="n">
-        <v>24600</v>
+        <v>26308</v>
       </c>
       <c r="C304" t="n">
-        <v>111.76</v>
+        <v>91.59</v>
       </c>
       <c r="D304" t="n">
-        <v>24921</v>
+        <v>28318</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>100.76</v>
+        <v>110.43</v>
       </c>
       <c r="B305" t="n">
-        <v>46429</v>
+        <v>26391</v>
       </c>
       <c r="C305" t="n">
-        <v>104.36</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="D305" t="n">
-        <v>25143</v>
+        <v>23877</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>100.2</v>
+        <v>111.61</v>
       </c>
       <c r="B306" t="n">
-        <v>46731</v>
+        <v>25524</v>
       </c>
       <c r="C306" t="n">
-        <v>104.7</v>
+        <v>106.04</v>
       </c>
       <c r="D306" t="n">
-        <v>25032</v>
+        <v>28322</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>109.98</v>
+        <v>112.04</v>
       </c>
       <c r="B307" t="n">
-        <v>32488</v>
+        <v>23131</v>
       </c>
       <c r="C307" t="n">
-        <v>106.32</v>
+        <v>113.57</v>
       </c>
       <c r="D307" t="n">
-        <v>25009</v>
+        <v>23766</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>97.93000000000001</v>
+        <v>112.16</v>
       </c>
       <c r="B308" t="n">
-        <v>42656</v>
+        <v>23078</v>
       </c>
       <c r="C308" t="n">
-        <v>97.79000000000001</v>
+        <v>103.58</v>
       </c>
       <c r="D308" t="n">
-        <v>24981</v>
+        <v>28177</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>110.46</v>
+        <v>112.34</v>
       </c>
       <c r="B309" t="n">
-        <v>31754</v>
+        <v>23839</v>
       </c>
       <c r="C309" t="n">
-        <v>106.88</v>
+        <v>91.39</v>
       </c>
       <c r="D309" t="n">
-        <v>23899</v>
+        <v>23913</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>159.02</v>
+        <v>113.11</v>
       </c>
       <c r="B310" t="n">
-        <v>24143</v>
+        <v>22937</v>
       </c>
       <c r="C310" t="n">
-        <v>155.46</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D310" t="n">
-        <v>24881</v>
+        <v>25042</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>101.45</v>
+        <v>113.48</v>
       </c>
       <c r="B311" t="n">
-        <v>47104</v>
+        <v>22548</v>
       </c>
       <c r="C311" t="n">
-        <v>98.79000000000001</v>
+        <v>132.29</v>
       </c>
       <c r="D311" t="n">
-        <v>25105</v>
+        <v>23742</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>35.83</v>
+        <v>113.7</v>
       </c>
       <c r="B312" t="n">
-        <v>24046</v>
+        <v>23296</v>
       </c>
       <c r="C312" t="n">
-        <v>36.87</v>
+        <v>92.41</v>
       </c>
       <c r="D312" t="n">
-        <v>28352</v>
+        <v>28262</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>103.5</v>
+        <v>113.73</v>
       </c>
       <c r="B313" t="n">
-        <v>48944</v>
+        <v>23840</v>
       </c>
       <c r="C313" t="n">
-        <v>103.42</v>
+        <v>104.78</v>
       </c>
       <c r="D313" t="n">
-        <v>23814</v>
+        <v>23917</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>90.98</v>
+        <v>114.49</v>
       </c>
       <c r="B314" t="n">
-        <v>26033</v>
+        <v>22791</v>
       </c>
       <c r="C314" t="n">
-        <v>91.56999999999999</v>
+        <v>132.82</v>
       </c>
       <c r="D314" t="n">
-        <v>23890</v>
+        <v>24944</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>92.45</v>
+        <v>114.56</v>
       </c>
       <c r="B315" t="n">
-        <v>26671</v>
+        <v>23567</v>
       </c>
       <c r="C315" t="n">
-        <v>93.39</v>
+        <v>119.38</v>
       </c>
       <c r="D315" t="n">
-        <v>23966</v>
+        <v>25010</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>93.41</v>
+        <v>115.51</v>
       </c>
       <c r="B316" t="n">
-        <v>32697</v>
+        <v>21655</v>
       </c>
       <c r="C316" t="n">
-        <v>96.59999999999999</v>
+        <v>121.31</v>
       </c>
       <c r="D316" t="n">
-        <v>23813</v>
+        <v>24860</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>115.56</v>
+        <v>116.05</v>
       </c>
       <c r="B317" t="n">
-        <v>24018</v>
+        <v>19226</v>
       </c>
       <c r="C317" t="n">
-        <v>118.42</v>
+        <v>148.59</v>
       </c>
       <c r="D317" t="n">
-        <v>24988</v>
+        <v>28224</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>101.65</v>
+        <v>116.06</v>
       </c>
       <c r="B318" t="n">
-        <v>48768</v>
+        <v>20605</v>
       </c>
       <c r="C318" t="n">
-        <v>101.71</v>
+        <v>112.81</v>
       </c>
       <c r="D318" t="n">
-        <v>25106</v>
+        <v>23846</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>93.28</v>
+        <v>116.44</v>
       </c>
       <c r="B319" t="n">
-        <v>31764</v>
+        <v>21242</v>
       </c>
       <c r="C319" t="n">
-        <v>91.27</v>
+        <v>119.87</v>
       </c>
       <c r="D319" t="n">
-        <v>28308</v>
+        <v>28159</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>91.13</v>
+        <v>117.11</v>
       </c>
       <c r="B320" t="n">
-        <v>24347</v>
+        <v>22854</v>
       </c>
       <c r="C320" t="n">
-        <v>92.92</v>
+        <v>129.26</v>
       </c>
       <c r="D320" t="n">
-        <v>23900</v>
+        <v>28263</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>113.82</v>
+        <v>117.72</v>
       </c>
       <c r="B321" t="n">
-        <v>29095</v>
+        <v>20121</v>
       </c>
       <c r="C321" t="n">
-        <v>112.3</v>
+        <v>106.51</v>
       </c>
       <c r="D321" t="n">
-        <v>28446</v>
+        <v>24944</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>107.36</v>
+        <v>117.73</v>
       </c>
       <c r="B322" t="n">
-        <v>45240</v>
+        <v>20425</v>
       </c>
       <c r="C322" t="n">
-        <v>110.64</v>
+        <v>102.24</v>
       </c>
       <c r="D322" t="n">
-        <v>28511</v>
+        <v>25038</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>109.83</v>
+        <v>118.39</v>
       </c>
       <c r="B323" t="n">
-        <v>33291</v>
+        <v>21674</v>
       </c>
       <c r="C323" t="n">
-        <v>105.99</v>
+        <v>115.84</v>
       </c>
       <c r="D323" t="n">
-        <v>25120</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>98.17</v>
+        <v>118.54</v>
       </c>
       <c r="B324" t="n">
-        <v>42438</v>
+        <v>19309</v>
       </c>
       <c r="C324" t="n">
-        <v>93.12</v>
+        <v>100.71</v>
       </c>
       <c r="D324" t="n">
-        <v>28350</v>
+        <v>28415</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>94.13</v>
+        <v>119.48</v>
       </c>
       <c r="B325" t="n">
-        <v>34305</v>
+        <v>20659</v>
       </c>
       <c r="C325" t="n">
-        <v>96.33</v>
+        <v>119.71</v>
       </c>
       <c r="D325" t="n">
-        <v>13.24</v>
+        <v>23942</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>111.08</v>
+        <v>119.53</v>
       </c>
       <c r="B326" t="n">
-        <v>32822</v>
+        <v>20371</v>
       </c>
       <c r="C326" t="n">
-        <v>112.27</v>
+        <v>140.59</v>
       </c>
       <c r="D326" t="n">
-        <v>13.24</v>
+        <v>25073</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>97.54000000000001</v>
+        <v>119.56</v>
       </c>
       <c r="B327" t="n">
-        <v>43195</v>
+        <v>21208</v>
       </c>
       <c r="C327" t="n">
-        <v>95.17</v>
+        <v>127.81</v>
       </c>
       <c r="D327" t="n">
-        <v>28274</v>
+        <v>23924</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>114.23</v>
+        <v>119.56</v>
       </c>
       <c r="B328" t="n">
-        <v>24761</v>
+        <v>20352</v>
       </c>
       <c r="C328" t="n">
-        <v>112.47</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="D328" t="n">
-        <v>28308</v>
+        <v>28186</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>111.97</v>
+        <v>119.73</v>
       </c>
       <c r="B329" t="n">
-        <v>27567</v>
+        <v>19096</v>
       </c>
       <c r="C329" t="n">
-        <v>110.01</v>
+        <v>137.95</v>
       </c>
       <c r="D329" t="n">
-        <v>23963</v>
+        <v>24022</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>111.64</v>
+        <v>119.83</v>
       </c>
       <c r="B330" t="n">
-        <v>28437</v>
+        <v>20272</v>
       </c>
       <c r="C330" t="n">
-        <v>111.36</v>
+        <v>145.46</v>
       </c>
       <c r="D330" t="n">
-        <v>25077</v>
+        <v>23916</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>153.85</v>
+        <v>120.13</v>
       </c>
       <c r="B331" t="n">
-        <v>27058</v>
+        <v>21565</v>
       </c>
       <c r="C331" t="n">
-        <v>148.88</v>
+        <v>117.52</v>
       </c>
       <c r="D331" t="n">
-        <v>23941</v>
+        <v>24080</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>99.59</v>
+        <v>120.15</v>
       </c>
       <c r="B332" t="n">
-        <v>45618</v>
+        <v>20864</v>
       </c>
       <c r="C332" t="n">
-        <v>95.73999999999999</v>
+        <v>137.94</v>
       </c>
       <c r="D332" t="n">
-        <v>24967</v>
+        <v>25099</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>110.45</v>
+        <v>120.29</v>
       </c>
       <c r="B333" t="n">
-        <v>33775</v>
+        <v>19525</v>
       </c>
       <c r="C333" t="n">
-        <v>114.28</v>
+        <v>144.54</v>
       </c>
       <c r="D333" t="n">
-        <v>24764</v>
+        <v>28191</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>99.18000000000001</v>
+        <v>120.38</v>
       </c>
       <c r="B334" t="n">
-        <v>45154</v>
+        <v>19528</v>
       </c>
       <c r="C334" t="n">
-        <v>100.03</v>
+        <v>141.46</v>
       </c>
       <c r="D334" t="n">
-        <v>25095</v>
+        <v>24985</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>96.48</v>
+        <v>120.47</v>
       </c>
       <c r="B335" t="n">
-        <v>38489</v>
+        <v>20787</v>
       </c>
       <c r="C335" t="n">
-        <v>94.78</v>
+        <v>116.96</v>
       </c>
       <c r="D335" t="n">
-        <v>28449</v>
+        <v>24114</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>96.51000000000001</v>
+        <v>120.77</v>
       </c>
       <c r="B336" t="n">
-        <v>38290</v>
+        <v>21810</v>
       </c>
       <c r="C336" t="n">
-        <v>96.06999999999999</v>
+        <v>114</v>
       </c>
       <c r="D336" t="n">
-        <v>23834</v>
+        <v>23881</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>97.01000000000001</v>
+        <v>121.12</v>
       </c>
       <c r="B337" t="n">
-        <v>41437</v>
+        <v>20513</v>
       </c>
       <c r="C337" t="n">
-        <v>94.28</v>
+        <v>133.28</v>
       </c>
       <c r="D337" t="n">
-        <v>23987</v>
+        <v>24958</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>106.74</v>
+        <v>121.18</v>
       </c>
       <c r="B338" t="n">
-        <v>45161</v>
+        <v>20580</v>
       </c>
       <c r="C338" t="n">
-        <v>107.92</v>
+        <v>127.16</v>
       </c>
       <c r="D338" t="n">
-        <v>24881</v>
+        <v>23843</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>101.46</v>
+        <v>121.29</v>
       </c>
       <c r="B339" t="n">
-        <v>48800</v>
+        <v>20266</v>
       </c>
       <c r="C339" t="n">
-        <v>99.3</v>
+        <v>142.23</v>
       </c>
       <c r="D339" t="n">
-        <v>23849</v>
+        <v>24011</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>94.84999999999999</v>
+        <v>121.49</v>
       </c>
       <c r="B340" t="n">
-        <v>34462</v>
+        <v>20995</v>
       </c>
       <c r="C340" t="n">
-        <v>94.28</v>
+        <v>119.69</v>
       </c>
       <c r="D340" t="n">
-        <v>25064</v>
+        <v>28367</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>98.89</v>
+        <v>121.64</v>
       </c>
       <c r="B341" t="n">
-        <v>42045</v>
+        <v>21776</v>
       </c>
       <c r="C341" t="n">
-        <v>96.52</v>
+        <v>113.22</v>
       </c>
       <c r="D341" t="n">
-        <v>23912</v>
+        <v>28148</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>90.41</v>
+        <v>122.07</v>
       </c>
       <c r="B342" t="n">
-        <v>25219</v>
+        <v>20028</v>
       </c>
       <c r="C342" t="n">
-        <v>89.20999999999999</v>
+        <v>106.03</v>
       </c>
       <c r="D342" t="n">
-        <v>24006</v>
+        <v>28365</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>111.65</v>
+        <v>122.19</v>
       </c>
       <c r="B343" t="n">
-        <v>26809</v>
+        <v>19367</v>
       </c>
       <c r="C343" t="n">
-        <v>108.65</v>
+        <v>139.49</v>
       </c>
       <c r="D343" t="n">
-        <v>23805</v>
+        <v>23917</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>93.22</v>
+        <v>122.36</v>
       </c>
       <c r="B344" t="n">
-        <v>31195</v>
+        <v>18121</v>
       </c>
       <c r="C344" t="n">
-        <v>90.31999999999999</v>
+        <v>123.89</v>
       </c>
       <c r="D344" t="n">
-        <v>24981</v>
+        <v>28151</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>113.94</v>
+        <v>122.37</v>
       </c>
       <c r="B345" t="n">
-        <v>26759</v>
+        <v>19886</v>
       </c>
       <c r="C345" t="n">
-        <v>114.68</v>
+        <v>122.51</v>
       </c>
       <c r="D345" t="n">
-        <v>13.76</v>
+        <v>28330</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>149.36</v>
+        <v>123.85</v>
       </c>
       <c r="B346" t="n">
-        <v>24687</v>
+        <v>19998</v>
       </c>
       <c r="C346" t="n">
-        <v>152.83</v>
+        <v>122.15</v>
       </c>
       <c r="D346" t="n">
-        <v>25033</v>
+        <v>28200</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>97.22</v>
+        <v>124.01</v>
       </c>
       <c r="B347" t="n">
-        <v>41391</v>
+        <v>22301</v>
       </c>
       <c r="C347" t="n">
-        <v>100.82</v>
+        <v>148.46</v>
       </c>
       <c r="D347" t="n">
-        <v>13.36</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>98.61</v>
+        <v>124.19</v>
       </c>
       <c r="B348" t="n">
-        <v>45102</v>
+        <v>20869</v>
       </c>
       <c r="C348" t="n">
-        <v>97.94</v>
+        <v>141.99</v>
       </c>
       <c r="D348" t="n">
-        <v>23826</v>
+        <v>23844</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>96.34</v>
+        <v>124.3</v>
       </c>
       <c r="B349" t="n">
-        <v>40331</v>
+        <v>19737</v>
       </c>
       <c r="C349" t="n">
-        <v>99.95999999999999</v>
+        <v>125.54</v>
       </c>
       <c r="D349" t="n">
-        <v>23874</v>
+        <v>25044</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>109.14</v>
+        <v>124.35</v>
       </c>
       <c r="B350" t="n">
-        <v>36550</v>
+        <v>17271</v>
       </c>
       <c r="C350" t="n">
-        <v>107.39</v>
+        <v>152.97</v>
       </c>
       <c r="D350" t="n">
-        <v>25005</v>
+        <v>28365</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>101.86</v>
+        <v>124.96</v>
       </c>
       <c r="B351" t="n">
-        <v>50528</v>
+        <v>19681</v>
       </c>
       <c r="C351" t="n">
-        <v>101.03</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="D351" t="n">
-        <v>28431</v>
+        <v>24975</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>91.38</v>
+        <v>126.66</v>
       </c>
       <c r="B352" t="n">
-        <v>25856</v>
+        <v>20175</v>
       </c>
       <c r="C352" t="n">
-        <v>94.7</v>
+        <v>103.17</v>
       </c>
       <c r="D352" t="n">
-        <v>25115</v>
+        <v>23881</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>86.42</v>
+        <v>126.99</v>
       </c>
       <c r="B353" t="n">
-        <v>25114</v>
+        <v>20333</v>
       </c>
       <c r="C353" t="n">
-        <v>85.3</v>
+        <v>130.09</v>
       </c>
       <c r="D353" t="n">
-        <v>23952</v>
+        <v>24920</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>106.96</v>
+        <v>127.5</v>
       </c>
       <c r="B354" t="n">
-        <v>42026</v>
+        <v>20031</v>
       </c>
       <c r="C354" t="n">
-        <v>103.6</v>
+        <v>99.19</v>
       </c>
       <c r="D354" t="n">
-        <v>25037</v>
+        <v>23937</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>101.54</v>
+        <v>127.63</v>
       </c>
       <c r="B355" t="n">
-        <v>49234</v>
+        <v>20092</v>
       </c>
       <c r="C355" t="n">
-        <v>100.87</v>
+        <v>156.81</v>
       </c>
       <c r="D355" t="n">
-        <v>13.41</v>
+        <v>25103</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>98.11</v>
+        <v>127.81</v>
       </c>
       <c r="B356" t="n">
-        <v>43214</v>
+        <v>20266</v>
       </c>
       <c r="C356" t="n">
-        <v>99.73999999999999</v>
+        <v>144.51</v>
       </c>
       <c r="D356" t="n">
-        <v>23970</v>
+        <v>25094</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>98.81999999999999</v>
+        <v>128.23</v>
       </c>
       <c r="B357" t="n">
-        <v>43519</v>
+        <v>21728</v>
       </c>
       <c r="C357" t="n">
-        <v>97</v>
+        <v>150.37</v>
       </c>
       <c r="D357" t="n">
-        <v>23902</v>
+        <v>28103</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>95.98999999999999</v>
+        <v>128.59</v>
       </c>
       <c r="B358" t="n">
-        <v>38137</v>
+        <v>17246</v>
       </c>
       <c r="C358" t="n">
-        <v>93.56</v>
+        <v>129.17</v>
       </c>
       <c r="D358" t="n">
-        <v>23902</v>
+        <v>23897</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>93.83</v>
+        <v>129.18</v>
       </c>
       <c r="B359" t="n">
-        <v>31247</v>
+        <v>19222</v>
       </c>
       <c r="C359" t="n">
-        <v>93.2</v>
+        <v>129.98</v>
       </c>
       <c r="D359" t="n">
-        <v>28147</v>
+        <v>27970</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>107.27</v>
+        <v>129.83</v>
       </c>
       <c r="B360" t="n">
-        <v>40962</v>
+        <v>21050</v>
       </c>
       <c r="C360" t="n">
-        <v>106.95</v>
+        <v>122.36</v>
       </c>
       <c r="D360" t="n">
-        <v>23922</v>
+        <v>23829</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>111.8</v>
+        <v>130.1</v>
       </c>
       <c r="B361" t="n">
-        <v>31355</v>
+        <v>20508</v>
       </c>
       <c r="C361" t="n">
-        <v>114.24</v>
+        <v>145.89</v>
       </c>
       <c r="D361" t="n">
-        <v>13.98</v>
+        <v>23821</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>105.55</v>
+        <v>130.72</v>
       </c>
       <c r="B362" t="n">
-        <v>46950</v>
+        <v>20906</v>
       </c>
       <c r="C362" t="n">
-        <v>105.33</v>
+        <v>139.61</v>
       </c>
       <c r="D362" t="n">
-        <v>23832</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>109.43</v>
+        <v>131.77</v>
       </c>
       <c r="B363" t="n">
-        <v>38469</v>
+        <v>19395</v>
       </c>
       <c r="C363" t="n">
-        <v>105.08</v>
+        <v>149.37</v>
       </c>
       <c r="D363" t="n">
-        <v>28271</v>
+        <v>23748</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>95.87</v>
+        <v>132.02</v>
       </c>
       <c r="B364" t="n">
-        <v>37087</v>
+        <v>21045</v>
       </c>
       <c r="C364" t="n">
-        <v>94.19</v>
+        <v>153.61</v>
       </c>
       <c r="D364" t="n">
-        <v>25041</v>
+        <v>28280</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>101.17</v>
+        <v>132.4</v>
       </c>
       <c r="B365" t="n">
-        <v>46000</v>
+        <v>16825</v>
       </c>
       <c r="C365" t="n">
-        <v>101.41</v>
+        <v>149.76</v>
       </c>
       <c r="D365" t="n">
-        <v>24014</v>
+        <v>23961</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>103.5</v>
+        <v>132.46</v>
       </c>
       <c r="B366" t="n">
-        <v>47963</v>
+        <v>20434</v>
       </c>
       <c r="C366" t="n">
-        <v>104.75</v>
+        <v>139.82</v>
       </c>
       <c r="D366" t="n">
-        <v>23919</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>103.88</v>
+        <v>132.88</v>
       </c>
       <c r="B367" t="n">
-        <v>48434</v>
+        <v>19397</v>
       </c>
       <c r="C367" t="n">
-        <v>106.07</v>
+        <v>105.35</v>
       </c>
       <c r="D367" t="n">
-        <v>24934</v>
+        <v>23971</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>107.71</v>
+        <v>133.7</v>
       </c>
       <c r="B368" t="n">
-        <v>38886</v>
+        <v>20472</v>
       </c>
       <c r="C368" t="n">
-        <v>109.43</v>
+        <v>148.11</v>
       </c>
       <c r="D368" t="n">
-        <v>28117</v>
+        <v>28322</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>109.02</v>
+        <v>133.8</v>
       </c>
       <c r="B369" t="n">
-        <v>37811</v>
+        <v>21614</v>
       </c>
       <c r="C369" t="n">
-        <v>106.01</v>
+        <v>116.76</v>
       </c>
       <c r="D369" t="n">
-        <v>23777</v>
+        <v>23984</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>92.94</v>
+        <v>134.16</v>
       </c>
       <c r="B370" t="n">
-        <v>27691</v>
+        <v>21228</v>
       </c>
       <c r="C370" t="n">
-        <v>97.95</v>
+        <v>137.55</v>
       </c>
       <c r="D370" t="n">
-        <v>13.41</v>
+        <v>23961</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>107.97</v>
+        <v>134.32</v>
       </c>
       <c r="B371" t="n">
-        <v>36103</v>
+        <v>19955</v>
       </c>
       <c r="C371" t="n">
-        <v>106.96</v>
+        <v>161.6</v>
       </c>
       <c r="D371" t="n">
-        <v>13.98</v>
+        <v>28046</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>91.48999999999999</v>
+        <v>134.36</v>
       </c>
       <c r="B372" t="n">
-        <v>26705</v>
+        <v>19054</v>
       </c>
       <c r="C372" t="n">
-        <v>89.25</v>
+        <v>151.07</v>
       </c>
       <c r="D372" t="n">
-        <v>23937</v>
+        <v>25031</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>100.66</v>
+        <v>134.9</v>
       </c>
       <c r="B373" t="n">
-        <v>46439</v>
+        <v>19466</v>
       </c>
       <c r="C373" t="n">
-        <v>102.32</v>
+        <v>144.23</v>
       </c>
       <c r="D373" t="n">
-        <v>28246</v>
+        <v>24006</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>108.04</v>
+        <v>135.49</v>
       </c>
       <c r="B374" t="n">
-        <v>40529</v>
+        <v>21917</v>
       </c>
       <c r="C374" t="n">
-        <v>106.69</v>
+        <v>145.1</v>
       </c>
       <c r="D374" t="n">
-        <v>23982</v>
+        <v>25050</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>104.52</v>
+        <v>135.62</v>
       </c>
       <c r="B375" t="n">
-        <v>47261</v>
+        <v>20270</v>
       </c>
       <c r="C375" t="n">
-        <v>105.62</v>
+        <v>131.96</v>
       </c>
       <c r="D375" t="n">
-        <v>25083</v>
+        <v>23998</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>155.03</v>
+        <v>136.13</v>
       </c>
       <c r="B376" t="n">
-        <v>25669</v>
+        <v>20001</v>
       </c>
       <c r="C376" t="n">
-        <v>151.31</v>
+        <v>121.91</v>
       </c>
       <c r="D376" t="n">
-        <v>28291</v>
+        <v>25149</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>114.15</v>
+        <v>136.14</v>
       </c>
       <c r="B377" t="n">
-        <v>26240</v>
+        <v>18629</v>
       </c>
       <c r="C377" t="n">
-        <v>116.21</v>
+        <v>147.65</v>
       </c>
       <c r="D377" t="n">
-        <v>28118</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>121.42</v>
+        <v>136.38</v>
       </c>
       <c r="B378" t="n">
-        <v>25445</v>
+        <v>21561</v>
       </c>
       <c r="C378" t="n">
-        <v>122.25</v>
+        <v>136.72</v>
       </c>
       <c r="D378" t="n">
-        <v>24916</v>
+        <v>28404</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>105.89</v>
+        <v>136.45</v>
       </c>
       <c r="B379" t="n">
-        <v>48188</v>
+        <v>19738</v>
       </c>
       <c r="C379" t="n">
-        <v>102.88</v>
+        <v>157.38</v>
       </c>
       <c r="D379" t="n">
-        <v>24129</v>
+        <v>23822</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>93.51000000000001</v>
+        <v>137.06</v>
       </c>
       <c r="B380" t="n">
-        <v>28369</v>
+        <v>18408</v>
       </c>
       <c r="C380" t="n">
-        <v>95.36</v>
+        <v>121.47</v>
       </c>
       <c r="D380" t="n">
-        <v>28252</v>
+        <v>28410</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>108.47</v>
+        <v>137.22</v>
       </c>
       <c r="B381" t="n">
-        <v>38930</v>
+        <v>19920</v>
       </c>
       <c r="C381" t="n">
-        <v>110.05</v>
+        <v>131.82</v>
       </c>
       <c r="D381" t="n">
-        <v>25082</v>
+        <v>28219</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>24.11</v>
+        <v>137.73</v>
       </c>
       <c r="B382" t="n">
-        <v>24982</v>
+        <v>17580</v>
       </c>
       <c r="C382" t="n">
-        <v>24.92</v>
+        <v>106.24</v>
       </c>
       <c r="D382" t="n">
-        <v>23963</v>
+        <v>28228</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>94.47</v>
+        <v>137.79</v>
       </c>
       <c r="B383" t="n">
-        <v>35449</v>
+        <v>21243</v>
       </c>
       <c r="C383" t="n">
-        <v>92.12</v>
+        <v>156.12</v>
       </c>
       <c r="D383" t="n">
-        <v>23915</v>
+        <v>24972</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>105.65</v>
+        <v>137.98</v>
       </c>
       <c r="B384" t="n">
-        <v>46581</v>
+        <v>17674</v>
       </c>
       <c r="C384" t="n">
-        <v>103.39</v>
+        <v>152.92</v>
       </c>
       <c r="D384" t="n">
-        <v>28085</v>
+        <v>28358</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>93.05</v>
+        <v>138.11</v>
       </c>
       <c r="B385" t="n">
-        <v>30312</v>
+        <v>21902</v>
       </c>
       <c r="C385" t="n">
-        <v>94.02</v>
+        <v>154.14</v>
       </c>
       <c r="D385" t="n">
-        <v>24089</v>
+        <v>28138</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>101.85</v>
+        <v>138.46</v>
       </c>
       <c r="B386" t="n">
-        <v>49825</v>
+        <v>21594</v>
       </c>
       <c r="C386" t="n">
-        <v>104.52</v>
+        <v>128.69</v>
       </c>
       <c r="D386" t="n">
-        <v>24918</v>
+        <v>28305</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>97.15000000000001</v>
+        <v>138.53</v>
       </c>
       <c r="B387" t="n">
-        <v>43307</v>
+        <v>18307</v>
       </c>
       <c r="C387" t="n">
-        <v>96.22</v>
+        <v>159.91</v>
       </c>
       <c r="D387" t="n">
-        <v>28439</v>
+        <v>24702</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>16.81</v>
+        <v>138.9</v>
       </c>
       <c r="B388" t="n">
-        <v>26780</v>
+        <v>19381</v>
       </c>
       <c r="C388" t="n">
-        <v>17.06</v>
+        <v>137.9</v>
       </c>
       <c r="D388" t="n">
-        <v>28181</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>106.21</v>
+        <v>138.96</v>
       </c>
       <c r="B389" t="n">
-        <v>47114</v>
+        <v>22252</v>
       </c>
       <c r="C389" t="n">
-        <v>104.45</v>
+        <v>129.14</v>
       </c>
       <c r="D389" t="n">
-        <v>13.98</v>
+        <v>28252</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>110.23</v>
+        <v>139.01</v>
       </c>
       <c r="B390" t="n">
-        <v>33208</v>
+        <v>19246</v>
       </c>
       <c r="C390" t="n">
-        <v>112.38</v>
+        <v>125.35</v>
       </c>
       <c r="D390" t="n">
-        <v>28175</v>
+        <v>24844</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>108.63</v>
+        <v>139.27</v>
       </c>
       <c r="B391" t="n">
-        <v>38229</v>
+        <v>20610</v>
       </c>
       <c r="C391" t="n">
-        <v>105.71</v>
+        <v>153.86</v>
       </c>
       <c r="D391" t="n">
-        <v>28285</v>
+        <v>23913</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>102.96</v>
+        <v>139.54</v>
       </c>
       <c r="B392" t="n">
-        <v>49251</v>
+        <v>18884</v>
       </c>
       <c r="C392" t="n">
-        <v>102.77</v>
+        <v>115.03</v>
       </c>
       <c r="D392" t="n">
-        <v>13.41</v>
+        <v>28161</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>133.03</v>
+        <v>139.84</v>
       </c>
       <c r="B393" t="n">
-        <v>24415</v>
+        <v>22525</v>
       </c>
       <c r="C393" t="n">
-        <v>134.88</v>
+        <v>130.18</v>
       </c>
       <c r="D393" t="n">
-        <v>28386</v>
+        <v>28188</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>97.92</v>
+        <v>140.04</v>
       </c>
       <c r="B394" t="n">
-        <v>43491</v>
+        <v>22117</v>
       </c>
       <c r="C394" t="n">
-        <v>95.39</v>
+        <v>155.25</v>
       </c>
       <c r="D394" t="n">
-        <v>24882</v>
+        <v>28040</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>98.02</v>
+        <v>140.35</v>
       </c>
       <c r="B395" t="n">
-        <v>41187</v>
+        <v>17954</v>
       </c>
       <c r="C395" t="n">
-        <v>99.84999999999999</v>
+        <v>148</v>
       </c>
       <c r="D395" t="n">
-        <v>28242</v>
+        <v>25116</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>110.86</v>
+        <v>140.4</v>
       </c>
       <c r="B396" t="n">
-        <v>32079</v>
+        <v>18111</v>
       </c>
       <c r="C396" t="n">
-        <v>112.89</v>
+        <v>114.84</v>
       </c>
       <c r="D396" t="n">
-        <v>13.76</v>
+        <v>25085</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>96.02</v>
+        <v>141.04</v>
       </c>
       <c r="B397" t="n">
-        <v>39684</v>
+        <v>22209</v>
       </c>
       <c r="C397" t="n">
-        <v>98.93000000000001</v>
+        <v>144.65</v>
       </c>
       <c r="D397" t="n">
-        <v>13.98</v>
+        <v>25014</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>113.75</v>
+        <v>141.18</v>
       </c>
       <c r="B398" t="n">
-        <v>27542</v>
+        <v>18657</v>
       </c>
       <c r="C398" t="n">
-        <v>112.28</v>
+        <v>158.62</v>
       </c>
       <c r="D398" t="n">
-        <v>28371</v>
+        <v>25099</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>90.31999999999999</v>
+        <v>141.42</v>
       </c>
       <c r="B399" t="n">
-        <v>24999</v>
+        <v>20691</v>
       </c>
       <c r="C399" t="n">
-        <v>92.45</v>
+        <v>115.83</v>
       </c>
       <c r="D399" t="n">
-        <v>13.41</v>
+        <v>28354</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>153.75</v>
+        <v>141.75</v>
       </c>
       <c r="B400" t="n">
-        <v>26184</v>
+        <v>22810</v>
       </c>
       <c r="C400" t="n">
-        <v>153.03</v>
+        <v>156.42</v>
       </c>
       <c r="D400" t="n">
-        <v>25110</v>
+        <v>24122</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>98.83</v>
+        <v>142.9</v>
       </c>
       <c r="B401" t="n">
-        <v>45089</v>
+        <v>20316</v>
       </c>
       <c r="C401" t="n">
-        <v>97.79000000000001</v>
+        <v>159.8</v>
       </c>
       <c r="D401" t="n">
-        <v>24952</v>
+        <v>28455</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>90.26000000000001</v>
+        <v>142.97</v>
       </c>
       <c r="B402" t="n">
-        <v>26087</v>
+        <v>22483</v>
       </c>
       <c r="C402" t="n">
-        <v>90.91</v>
+        <v>121</v>
       </c>
       <c r="D402" t="n">
-        <v>24916</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>104.17</v>
+        <v>143.25</v>
       </c>
       <c r="B403" t="n">
-        <v>48140</v>
+        <v>18746</v>
       </c>
       <c r="C403" t="n">
-        <v>100.86</v>
+        <v>145.13</v>
       </c>
       <c r="D403" t="n">
-        <v>13.24</v>
+        <v>23831</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>104.63</v>
+        <v>143.27</v>
       </c>
       <c r="B404" t="n">
-        <v>48069</v>
+        <v>20921</v>
       </c>
       <c r="C404" t="n">
-        <v>102.01</v>
+        <v>112.27</v>
       </c>
       <c r="D404" t="n">
-        <v>25109</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>20.17</v>
+        <v>143.4</v>
       </c>
       <c r="B405" t="n">
-        <v>26134</v>
+        <v>21882</v>
       </c>
       <c r="C405" t="n">
-        <v>19.93</v>
+        <v>148.86</v>
       </c>
       <c r="D405" t="n">
-        <v>23988</v>
+        <v>24050</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>93.56999999999999</v>
+        <v>144.08</v>
       </c>
       <c r="B406" t="n">
-        <v>30292</v>
+        <v>19144</v>
       </c>
       <c r="C406" t="n">
-        <v>95.20999999999999</v>
+        <v>113.43</v>
       </c>
       <c r="D406" t="n">
-        <v>13.36</v>
+        <v>24895</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>101.91</v>
+        <v>144.23</v>
       </c>
       <c r="B407" t="n">
-        <v>48319</v>
+        <v>21743</v>
       </c>
       <c r="C407" t="n">
-        <v>100.38</v>
+        <v>145.24</v>
       </c>
       <c r="D407" t="n">
-        <v>13.41</v>
+        <v>23841</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>107.1</v>
+        <v>144.47</v>
       </c>
       <c r="B408" t="n">
-        <v>43301</v>
+        <v>20682</v>
       </c>
       <c r="C408" t="n">
-        <v>105.52</v>
+        <v>166.81</v>
       </c>
       <c r="D408" t="n">
-        <v>13.98</v>
+        <v>28448</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>62.27</v>
+        <v>144.85</v>
       </c>
       <c r="B409" t="n">
-        <v>25926</v>
+        <v>21536</v>
       </c>
       <c r="C409" t="n">
-        <v>60.58</v>
+        <v>134.74</v>
       </c>
       <c r="D409" t="n">
-        <v>24944</v>
+        <v>24764</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>109.19</v>
+        <v>145.27</v>
       </c>
       <c r="B410" t="n">
-        <v>37594</v>
+        <v>19856</v>
       </c>
       <c r="C410" t="n">
-        <v>111.56</v>
+        <v>149.63</v>
       </c>
       <c r="D410" t="n">
-        <v>28449</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>101.76</v>
+        <v>146.25</v>
       </c>
       <c r="B411" t="n">
-        <v>48258</v>
+        <v>21070</v>
       </c>
       <c r="C411" t="n">
-        <v>105.2</v>
+        <v>142.06</v>
       </c>
       <c r="D411" t="n">
-        <v>24981</v>
+        <v>24947</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>114.28</v>
+        <v>147.05</v>
       </c>
       <c r="B412" t="n">
-        <v>24915</v>
+        <v>18976</v>
       </c>
       <c r="C412" t="n">
-        <v>117</v>
+        <v>125.32</v>
       </c>
       <c r="D412" t="n">
-        <v>23812</v>
+        <v>23890</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>111.91</v>
+        <v>148.1</v>
       </c>
       <c r="B413" t="n">
-        <v>31433</v>
+        <v>20931</v>
       </c>
       <c r="C413" t="n">
-        <v>113.45</v>
+        <v>143.59</v>
       </c>
       <c r="D413" t="n">
-        <v>24847</v>
+        <v>23866</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>117.24</v>
+        <v>148.62</v>
       </c>
       <c r="B414" t="n">
-        <v>25239</v>
+        <v>25266</v>
       </c>
       <c r="C414" t="n">
-        <v>118.33</v>
+        <v>116.72</v>
       </c>
       <c r="D414" t="n">
-        <v>25189</v>
+        <v>28401</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>98.45999999999999</v>
+        <v>149.01</v>
       </c>
       <c r="B415" t="n">
-        <v>45274</v>
+        <v>22611</v>
       </c>
       <c r="C415" t="n">
-        <v>95.01000000000001</v>
+        <v>137.39</v>
       </c>
       <c r="D415" t="n">
-        <v>23984</v>
+        <v>28274</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>112.63</v>
+        <v>149.17</v>
       </c>
       <c r="B416" t="n">
-        <v>28542</v>
+        <v>23933</v>
       </c>
       <c r="C416" t="n">
-        <v>110.39</v>
+        <v>157.71</v>
       </c>
       <c r="D416" t="n">
-        <v>23696</v>
+        <v>23980</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>149.17</v>
+        <v>149.19</v>
       </c>
       <c r="B417" t="n">
-        <v>24099</v>
+        <v>23521</v>
       </c>
       <c r="C417" t="n">
-        <v>150.12</v>
+        <v>143.27</v>
       </c>
       <c r="D417" t="n">
-        <v>28157</v>
+        <v>24088</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>97.09</v>
+        <v>149.81</v>
       </c>
       <c r="B418" t="n">
-        <v>37645</v>
+        <v>26065</v>
       </c>
       <c r="C418" t="n">
-        <v>98.72</v>
+        <v>127.74</v>
       </c>
       <c r="D418" t="n">
-        <v>24869</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>111.37</v>
+        <v>149.83</v>
       </c>
       <c r="B419" t="n">
-        <v>30448</v>
+        <v>23653</v>
       </c>
       <c r="C419" t="n">
-        <v>114.8</v>
+        <v>165.26</v>
       </c>
       <c r="D419" t="n">
-        <v>24042</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>105.24</v>
+        <v>150.47</v>
       </c>
       <c r="B420" t="n">
-        <v>48612</v>
+        <v>25212</v>
       </c>
       <c r="C420" t="n">
-        <v>108.16</v>
+        <v>130.59</v>
       </c>
       <c r="D420" t="n">
-        <v>23987</v>
+        <v>25045</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>91.52</v>
+        <v>151.39</v>
       </c>
       <c r="B421" t="n">
-        <v>28590</v>
+        <v>24813</v>
       </c>
       <c r="C421" t="n">
-        <v>90.2</v>
+        <v>127.88</v>
       </c>
       <c r="D421" t="n">
-        <v>23990</v>
+        <v>23912</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>103.19</v>
+        <v>151.74</v>
       </c>
       <c r="B422" t="n">
-        <v>49950</v>
+        <v>23699</v>
       </c>
       <c r="C422" t="n">
-        <v>101.11</v>
+        <v>173.09</v>
       </c>
       <c r="D422" t="n">
-        <v>24080</v>
+        <v>28235</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>96.58</v>
+        <v>151.76</v>
       </c>
       <c r="B423" t="n">
-        <v>37565</v>
+        <v>25257</v>
       </c>
       <c r="C423" t="n">
-        <v>93.79000000000001</v>
+        <v>142.56</v>
       </c>
       <c r="D423" t="n">
-        <v>23844</v>
+        <v>28382</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>110.96</v>
+        <v>152.21</v>
       </c>
       <c r="B424" t="n">
-        <v>32480</v>
+        <v>22529</v>
       </c>
       <c r="C424" t="n">
-        <v>106.61</v>
+        <v>150.36</v>
       </c>
       <c r="D424" t="n">
-        <v>28061</v>
+        <v>28131</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>90.14</v>
+        <v>152.49</v>
       </c>
       <c r="B425" t="n">
-        <v>24934</v>
+        <v>25415</v>
       </c>
       <c r="C425" t="n">
-        <v>88.45</v>
+        <v>139.66</v>
       </c>
       <c r="D425" t="n">
-        <v>25087</v>
+        <v>24957</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>102.4</v>
+        <v>152.64</v>
       </c>
       <c r="B426" t="n">
-        <v>49514</v>
+        <v>25618</v>
       </c>
       <c r="C426" t="n">
-        <v>99.88</v>
+        <v>141.66</v>
       </c>
       <c r="D426" t="n">
-        <v>23948</v>
+        <v>28039</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>86.95</v>
+        <v>152.89</v>
       </c>
       <c r="B427" t="n">
-        <v>26669</v>
+        <v>26589</v>
       </c>
       <c r="C427" t="n">
-        <v>84.98</v>
+        <v>135.19</v>
       </c>
       <c r="D427" t="n">
-        <v>28262</v>
+        <v>25006</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>93.23</v>
+        <v>153.08</v>
       </c>
       <c r="B428" t="n">
-        <v>31015</v>
+        <v>27539</v>
       </c>
       <c r="C428" t="n">
-        <v>91.81999999999999</v>
+        <v>149.93</v>
       </c>
       <c r="D428" t="n">
-        <v>13.76</v>
+        <v>25083</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>99.8</v>
+        <v>154.13</v>
       </c>
       <c r="B429" t="n">
-        <v>43249</v>
+        <v>27512</v>
       </c>
       <c r="C429" t="n">
-        <v>96.76000000000001</v>
+        <v>153.88</v>
       </c>
       <c r="D429" t="n">
-        <v>13.24</v>
+        <v>24949</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>148.89</v>
+        <v>154.31</v>
       </c>
       <c r="B430" t="n">
-        <v>25454</v>
+        <v>29420</v>
       </c>
       <c r="C430" t="n">
-        <v>143.77</v>
+        <v>139.56</v>
       </c>
       <c r="D430" t="n">
-        <v>24045</v>
+        <v>28178</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>113.88</v>
+        <v>154.58</v>
       </c>
       <c r="B431" t="n">
-        <v>24841</v>
+        <v>30217</v>
       </c>
       <c r="C431" t="n">
-        <v>110.81</v>
+        <v>124.61</v>
       </c>
       <c r="D431" t="n">
-        <v>23666</v>
+        <v>28139</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>163.34</v>
+        <v>154.78</v>
       </c>
       <c r="B432" t="n">
-        <v>24618</v>
+        <v>29208</v>
       </c>
       <c r="C432" t="n">
-        <v>157.02</v>
+        <v>124.11</v>
       </c>
       <c r="D432" t="n">
         <v>13.76</v>
@@ -6486,968 +6486,968 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>93.36</v>
+        <v>154.94</v>
       </c>
       <c r="B433" t="n">
-        <v>31982</v>
+        <v>25161</v>
       </c>
       <c r="C433" t="n">
-        <v>91.64</v>
+        <v>118.66</v>
       </c>
       <c r="D433" t="n">
-        <v>25028</v>
+        <v>23974</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>110.08</v>
+        <v>155.01</v>
       </c>
       <c r="B434" t="n">
-        <v>34556</v>
+        <v>29010</v>
       </c>
       <c r="C434" t="n">
-        <v>106.24</v>
+        <v>170.88</v>
       </c>
       <c r="D434" t="n">
-        <v>28195</v>
+        <v>24901</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>101.78</v>
+        <v>157.03</v>
       </c>
       <c r="B435" t="n">
-        <v>46879</v>
+        <v>29433</v>
       </c>
       <c r="C435" t="n">
-        <v>101.61</v>
+        <v>157.28</v>
       </c>
       <c r="D435" t="n">
-        <v>28319</v>
+        <v>24998</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>99.03</v>
+        <v>157.28</v>
       </c>
       <c r="B436" t="n">
-        <v>42750</v>
+        <v>30115</v>
       </c>
       <c r="C436" t="n">
-        <v>99.58</v>
+        <v>177.07</v>
       </c>
       <c r="D436" t="n">
-        <v>28533</v>
+        <v>24976</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>98.93000000000001</v>
+        <v>158.47</v>
       </c>
       <c r="B437" t="n">
-        <v>45630</v>
+        <v>31387</v>
       </c>
       <c r="C437" t="n">
-        <v>99.45</v>
+        <v>179.59</v>
       </c>
       <c r="D437" t="n">
-        <v>24034</v>
+        <v>23717</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>100.65</v>
+        <v>158.58</v>
       </c>
       <c r="B438" t="n">
-        <v>47179</v>
+        <v>30510</v>
       </c>
       <c r="C438" t="n">
-        <v>101.18</v>
+        <v>157.88</v>
       </c>
       <c r="D438" t="n">
-        <v>24907</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>91.65000000000001</v>
+        <v>159.64</v>
       </c>
       <c r="B439" t="n">
-        <v>26663</v>
+        <v>29447</v>
       </c>
       <c r="C439" t="n">
-        <v>89.81999999999999</v>
+        <v>140.13</v>
       </c>
       <c r="D439" t="n">
-        <v>25151</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>35.22</v>
+        <v>159.99</v>
       </c>
       <c r="B440" t="n">
-        <v>26314</v>
+        <v>31763</v>
       </c>
       <c r="C440" t="n">
-        <v>34.97</v>
+        <v>139.15</v>
       </c>
       <c r="D440" t="n">
-        <v>24001</v>
+        <v>24841</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>103.3</v>
+        <v>160.79</v>
       </c>
       <c r="B441" t="n">
-        <v>50724</v>
+        <v>33298</v>
       </c>
       <c r="C441" t="n">
-        <v>100.27</v>
+        <v>180</v>
       </c>
       <c r="D441" t="n">
-        <v>23824</v>
+        <v>28371</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>6.84</v>
+        <v>160.85</v>
       </c>
       <c r="B442" t="n">
-        <v>28627</v>
+        <v>27875</v>
       </c>
       <c r="C442" t="n">
-        <v>6.48</v>
+        <v>156.85</v>
       </c>
       <c r="D442" t="n">
-        <v>25082</v>
+        <v>28399</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>92.31999999999999</v>
+        <v>161.66</v>
       </c>
       <c r="B443" t="n">
-        <v>30707</v>
+        <v>31463</v>
       </c>
       <c r="C443" t="n">
-        <v>95.87</v>
+        <v>180</v>
       </c>
       <c r="D443" t="n">
-        <v>13.98</v>
+        <v>28333</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>110.78</v>
+        <v>162.11</v>
       </c>
       <c r="B444" t="n">
-        <v>31867</v>
+        <v>29115</v>
       </c>
       <c r="C444" t="n">
-        <v>113.38</v>
+        <v>136.73</v>
       </c>
       <c r="D444" t="n">
-        <v>24015</v>
+        <v>23939</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>35.2</v>
+        <v>162.22</v>
       </c>
       <c r="B445" t="n">
-        <v>25096</v>
+        <v>31616</v>
       </c>
       <c r="C445" t="n">
-        <v>36.21</v>
+        <v>132.62</v>
       </c>
       <c r="D445" t="n">
-        <v>28415</v>
+        <v>23940</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>102.36</v>
+        <v>162.64</v>
       </c>
       <c r="B446" t="n">
-        <v>50542</v>
+        <v>30520</v>
       </c>
       <c r="C446" t="n">
-        <v>100.88</v>
+        <v>135.42</v>
       </c>
       <c r="D446" t="n">
-        <v>23972</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>93.45</v>
+        <v>163.42</v>
       </c>
       <c r="B447" t="n">
-        <v>29882</v>
+        <v>27229</v>
       </c>
       <c r="C447" t="n">
-        <v>95.06</v>
+        <v>180</v>
       </c>
       <c r="D447" t="n">
-        <v>24895</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>95.13</v>
+        <v>163.56</v>
       </c>
       <c r="B448" t="n">
-        <v>35521</v>
+        <v>30372</v>
       </c>
       <c r="C448" t="n">
-        <v>96.62</v>
+        <v>142.06</v>
       </c>
       <c r="D448" t="n">
-        <v>13.36</v>
+        <v>25039</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>97.09</v>
+        <v>164.23</v>
       </c>
       <c r="B449" t="n">
-        <v>42575</v>
+        <v>29512</v>
       </c>
       <c r="C449" t="n">
-        <v>99.8</v>
+        <v>137.56</v>
       </c>
       <c r="D449" t="n">
-        <v>25112</v>
+        <v>23764</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>97.77</v>
+        <v>164.34</v>
       </c>
       <c r="B450" t="n">
-        <v>43706</v>
+        <v>29161</v>
       </c>
       <c r="C450" t="n">
-        <v>101.05</v>
+        <v>177.5</v>
       </c>
       <c r="D450" t="n">
-        <v>28281</v>
+        <v>24958</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>115.36</v>
+        <v>165.13</v>
       </c>
       <c r="B451" t="n">
-        <v>25512</v>
+        <v>29399</v>
       </c>
       <c r="C451" t="n">
-        <v>117.36</v>
+        <v>143.36</v>
       </c>
       <c r="D451" t="n">
-        <v>23989</v>
+        <v>23930</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>96.19</v>
+        <v>165.59</v>
       </c>
       <c r="B452" t="n">
-        <v>38521</v>
+        <v>29816</v>
       </c>
       <c r="C452" t="n">
-        <v>93.94</v>
+        <v>173.27</v>
       </c>
       <c r="D452" t="n">
-        <v>13.24</v>
+        <v>23857</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>103.39</v>
+        <v>165.98</v>
       </c>
       <c r="B453" t="n">
-        <v>47220</v>
+        <v>28688</v>
       </c>
       <c r="C453" t="n">
-        <v>104.61</v>
+        <v>149.88</v>
       </c>
       <c r="D453" t="n">
-        <v>24914</v>
+        <v>25069</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>93.75</v>
+        <v>166.49</v>
       </c>
       <c r="B454" t="n">
-        <v>34987</v>
+        <v>26786</v>
       </c>
       <c r="C454" t="n">
-        <v>91.42</v>
+        <v>133.53</v>
       </c>
       <c r="D454" t="n">
-        <v>13.41</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>110.03</v>
+        <v>167.1</v>
       </c>
       <c r="B455" t="n">
-        <v>35291</v>
+        <v>23741</v>
       </c>
       <c r="C455" t="n">
-        <v>110.96</v>
+        <v>180</v>
       </c>
       <c r="D455" t="n">
-        <v>13.76</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>51.39</v>
+        <v>167.4</v>
       </c>
       <c r="B456" t="n">
-        <v>27387</v>
+        <v>25794</v>
       </c>
       <c r="C456" t="n">
-        <v>50</v>
+        <v>152.37</v>
       </c>
       <c r="D456" t="n">
-        <v>24029</v>
+        <v>24844</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>25.31</v>
+        <v>167.43</v>
       </c>
       <c r="B457" t="n">
-        <v>24884</v>
+        <v>23683</v>
       </c>
       <c r="C457" t="n">
-        <v>24.03</v>
+        <v>149.11</v>
       </c>
       <c r="D457" t="n">
-        <v>13.76</v>
+        <v>24069</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>108.77</v>
+        <v>167.51</v>
       </c>
       <c r="B458" t="n">
-        <v>38243</v>
+        <v>25158</v>
       </c>
       <c r="C458" t="n">
-        <v>111.59</v>
+        <v>141.6</v>
       </c>
       <c r="D458" t="n">
-        <v>25096</v>
+        <v>28507</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>97.67</v>
+        <v>167.65</v>
       </c>
       <c r="B459" t="n">
-        <v>44200</v>
+        <v>28601</v>
       </c>
       <c r="C459" t="n">
-        <v>100.29</v>
+        <v>180</v>
       </c>
       <c r="D459" t="n">
-        <v>23948</v>
+        <v>24151</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>79.36</v>
+        <v>167.8</v>
       </c>
       <c r="B460" t="n">
-        <v>26656</v>
+        <v>25477</v>
       </c>
       <c r="C460" t="n">
-        <v>80.23999999999999</v>
+        <v>180</v>
       </c>
       <c r="D460" t="n">
-        <v>13.24</v>
+        <v>23912</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>113.06</v>
+        <v>167.82</v>
       </c>
       <c r="B461" t="n">
-        <v>26127</v>
+        <v>23809</v>
       </c>
       <c r="C461" t="n">
-        <v>113.93</v>
+        <v>162.16</v>
       </c>
       <c r="D461" t="n">
-        <v>25003</v>
+        <v>24922</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>101.5</v>
+        <v>168.06</v>
       </c>
       <c r="B462" t="n">
-        <v>48432</v>
+        <v>24377</v>
       </c>
       <c r="C462" t="n">
-        <v>97.11</v>
+        <v>167.17</v>
       </c>
       <c r="D462" t="n">
-        <v>28292</v>
+        <v>24990</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>106.39</v>
+        <v>168.36</v>
       </c>
       <c r="B463" t="n">
-        <v>44481</v>
+        <v>24565</v>
       </c>
       <c r="C463" t="n">
-        <v>109.07</v>
+        <v>168.03</v>
       </c>
       <c r="D463" t="n">
-        <v>23811</v>
+        <v>25139</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>111.7</v>
+        <v>168.44</v>
       </c>
       <c r="B464" t="n">
-        <v>32182</v>
+        <v>23881</v>
       </c>
       <c r="C464" t="n">
-        <v>109.79</v>
+        <v>149.42</v>
       </c>
       <c r="D464" t="n">
-        <v>25129</v>
+        <v>24924</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>101.27</v>
+        <v>168.62</v>
       </c>
       <c r="B465" t="n">
-        <v>45985</v>
+        <v>24365</v>
       </c>
       <c r="C465" t="n">
-        <v>100.93</v>
+        <v>175.09</v>
       </c>
       <c r="D465" t="n">
-        <v>13.36</v>
+        <v>24066</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>113.94</v>
+        <v>169.07</v>
       </c>
       <c r="B466" t="n">
-        <v>25939</v>
+        <v>23248</v>
       </c>
       <c r="C466" t="n">
-        <v>114.71</v>
+        <v>180</v>
       </c>
       <c r="D466" t="n">
-        <v>28213</v>
+        <v>23960</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>73.45</v>
+        <v>169.14</v>
       </c>
       <c r="B467" t="n">
-        <v>25920</v>
+        <v>24969</v>
       </c>
       <c r="C467" t="n">
-        <v>74.87</v>
+        <v>167.07</v>
       </c>
       <c r="D467" t="n">
-        <v>25074</v>
+        <v>23844</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>104.96</v>
+        <v>169.58</v>
       </c>
       <c r="B468" t="n">
-        <v>47110</v>
+        <v>23056</v>
       </c>
       <c r="C468" t="n">
-        <v>104.06</v>
+        <v>168.89</v>
       </c>
       <c r="D468" t="n">
-        <v>23926</v>
+        <v>28209</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>91.5</v>
+        <v>169.84</v>
       </c>
       <c r="B469" t="n">
-        <v>26329</v>
+        <v>24316</v>
       </c>
       <c r="C469" t="n">
-        <v>91.73999999999999</v>
+        <v>180</v>
       </c>
       <c r="D469" t="n">
-        <v>24945</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>111.5</v>
+        <v>170.58</v>
       </c>
       <c r="B470" t="n">
-        <v>30898</v>
+        <v>22933</v>
       </c>
       <c r="C470" t="n">
-        <v>115.13</v>
+        <v>163.97</v>
       </c>
       <c r="D470" t="n">
-        <v>23934</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>93.05</v>
+        <v>171.15</v>
       </c>
       <c r="B471" t="n">
-        <v>31482</v>
+        <v>24157</v>
       </c>
       <c r="C471" t="n">
-        <v>93.59999999999999</v>
+        <v>164.73</v>
       </c>
       <c r="D471" t="n">
-        <v>28385</v>
+        <v>25070</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>104.84</v>
+        <v>172.46</v>
       </c>
       <c r="B472" t="n">
-        <v>48680</v>
+        <v>21326</v>
       </c>
       <c r="C472" t="n">
-        <v>104.34</v>
+        <v>169.77</v>
       </c>
       <c r="D472" t="n">
-        <v>23924</v>
+        <v>28166</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>114.15</v>
+        <v>172.47</v>
       </c>
       <c r="B473" t="n">
-        <v>23076</v>
+        <v>20790</v>
       </c>
       <c r="C473" t="n">
-        <v>109.39</v>
+        <v>167.08</v>
       </c>
       <c r="D473" t="n">
-        <v>28313</v>
+        <v>28224</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>100.72</v>
+        <v>172.96</v>
       </c>
       <c r="B474" t="n">
-        <v>48181</v>
+        <v>20698</v>
       </c>
       <c r="C474" t="n">
-        <v>99.5</v>
+        <v>137.47</v>
       </c>
       <c r="D474" t="n">
-        <v>28094</v>
+        <v>23754</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>93.34</v>
+        <v>173.05</v>
       </c>
       <c r="B475" t="n">
-        <v>29476</v>
+        <v>19012</v>
       </c>
       <c r="C475" t="n">
-        <v>91.18000000000001</v>
+        <v>174.23</v>
       </c>
       <c r="D475" t="n">
-        <v>24970</v>
+        <v>24118</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>97.63</v>
+        <v>173.09</v>
       </c>
       <c r="B476" t="n">
-        <v>41014</v>
+        <v>19760</v>
       </c>
       <c r="C476" t="n">
-        <v>96.31999999999999</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>28141</v>
+        <v>23951</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>99.27</v>
+        <v>173.24</v>
       </c>
       <c r="B477" t="n">
-        <v>48538</v>
+        <v>17365</v>
       </c>
       <c r="C477" t="n">
-        <v>97.14</v>
+        <v>180</v>
       </c>
       <c r="D477" t="n">
-        <v>13.76</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>92.73</v>
+        <v>173.39</v>
       </c>
       <c r="B478" t="n">
-        <v>29559</v>
+        <v>18539</v>
       </c>
       <c r="C478" t="n">
-        <v>97.34</v>
+        <v>180</v>
       </c>
       <c r="D478" t="n">
-        <v>28136</v>
+        <v>28375</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>39.67</v>
+        <v>173.9</v>
       </c>
       <c r="B479" t="n">
-        <v>25902</v>
+        <v>18989</v>
       </c>
       <c r="C479" t="n">
-        <v>39.9</v>
+        <v>180</v>
       </c>
       <c r="D479" t="n">
-        <v>24868</v>
+        <v>24933</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>38.93</v>
+        <v>173.99</v>
       </c>
       <c r="B480" t="n">
-        <v>24723</v>
+        <v>19235</v>
       </c>
       <c r="C480" t="n">
-        <v>39.22</v>
+        <v>180</v>
       </c>
       <c r="D480" t="n">
-        <v>28205</v>
+        <v>24871</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>99.79000000000001</v>
+        <v>174</v>
       </c>
       <c r="B481" t="n">
-        <v>45387</v>
+        <v>21598</v>
       </c>
       <c r="C481" t="n">
-        <v>95.87</v>
+        <v>180</v>
       </c>
       <c r="D481" t="n">
-        <v>23914</v>
+        <v>28286</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>95.31999999999999</v>
+        <v>174.07</v>
       </c>
       <c r="B482" t="n">
-        <v>37157</v>
+        <v>20601</v>
       </c>
       <c r="C482" t="n">
-        <v>91.95</v>
+        <v>180</v>
       </c>
       <c r="D482" t="n">
-        <v>24976</v>
+        <v>25198</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>108.63</v>
+        <v>174.13</v>
       </c>
       <c r="B483" t="n">
-        <v>40248</v>
+        <v>21546</v>
       </c>
       <c r="C483" t="n">
-        <v>107.9</v>
+        <v>179.41</v>
       </c>
       <c r="D483" t="n">
-        <v>23985</v>
+        <v>24031</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>104.76</v>
+        <v>174.16</v>
       </c>
       <c r="B484" t="n">
-        <v>49015</v>
+        <v>20527</v>
       </c>
       <c r="C484" t="n">
-        <v>107.6</v>
+        <v>180</v>
       </c>
       <c r="D484" t="n">
-        <v>28228</v>
+        <v>25039</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>91.23</v>
+        <v>174.42</v>
       </c>
       <c r="B485" t="n">
-        <v>27632</v>
+        <v>20093</v>
       </c>
       <c r="C485" t="n">
-        <v>92.38</v>
+        <v>151.37</v>
       </c>
       <c r="D485" t="n">
-        <v>13.98</v>
+        <v>28217</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>92.28</v>
+        <v>174.62</v>
       </c>
       <c r="B486" t="n">
-        <v>30009</v>
+        <v>20403</v>
       </c>
       <c r="C486" t="n">
-        <v>95.43000000000001</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>13.41</v>
+        <v>24970</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>101.19</v>
+        <v>175.5</v>
       </c>
       <c r="B487" t="n">
-        <v>47414</v>
+        <v>19447</v>
       </c>
       <c r="C487" t="n">
-        <v>101.82</v>
+        <v>180</v>
       </c>
       <c r="D487" t="n">
-        <v>23962</v>
+        <v>23917</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>92.86</v>
+        <v>175.84</v>
       </c>
       <c r="B488" t="n">
-        <v>29351</v>
+        <v>19968</v>
       </c>
       <c r="C488" t="n">
-        <v>91.81999999999999</v>
+        <v>180</v>
       </c>
       <c r="D488" t="n">
-        <v>25047</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>91.64</v>
+        <v>175.87</v>
       </c>
       <c r="B489" t="n">
-        <v>27869</v>
+        <v>18974</v>
       </c>
       <c r="C489" t="n">
-        <v>90.38</v>
+        <v>177.56</v>
       </c>
       <c r="D489" t="n">
-        <v>13.36</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>108.34</v>
+        <v>175.9</v>
       </c>
       <c r="B490" t="n">
-        <v>37202</v>
+        <v>21901</v>
       </c>
       <c r="C490" t="n">
-        <v>110.69</v>
+        <v>180</v>
       </c>
       <c r="D490" t="n">
-        <v>25030</v>
+        <v>23979</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>104.82</v>
+        <v>176.25</v>
       </c>
       <c r="B491" t="n">
-        <v>48974</v>
+        <v>20604</v>
       </c>
       <c r="C491" t="n">
-        <v>105.01</v>
+        <v>180</v>
       </c>
       <c r="D491" t="n">
-        <v>28344</v>
+        <v>23759</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>93.25</v>
+        <v>176.41</v>
       </c>
       <c r="B492" t="n">
-        <v>33094</v>
+        <v>18436</v>
       </c>
       <c r="C492" t="n">
-        <v>90.79000000000001</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>28399</v>
+        <v>23720</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>102.74</v>
+        <v>177.05</v>
       </c>
       <c r="B493" t="n">
-        <v>48568</v>
+        <v>19842</v>
       </c>
       <c r="C493" t="n">
-        <v>105.62</v>
+        <v>146.77</v>
       </c>
       <c r="D493" t="n">
-        <v>24880</v>
+        <v>23780</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>92.41</v>
+        <v>177.36</v>
       </c>
       <c r="B494" t="n">
-        <v>30551</v>
+        <v>17509</v>
       </c>
       <c r="C494" t="n">
-        <v>95.53</v>
+        <v>142.77</v>
       </c>
       <c r="D494" t="n">
-        <v>13.24</v>
+        <v>24989</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>106.1</v>
+        <v>177.46</v>
       </c>
       <c r="B495" t="n">
-        <v>45483</v>
+        <v>19526</v>
       </c>
       <c r="C495" t="n">
-        <v>105.58</v>
+        <v>180</v>
       </c>
       <c r="D495" t="n">
-        <v>13.76</v>
+        <v>28125</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>145.97</v>
+        <v>177.46</v>
       </c>
       <c r="B496" t="n">
-        <v>22422</v>
+        <v>18947</v>
       </c>
       <c r="C496" t="n">
-        <v>146.4</v>
+        <v>142.34</v>
       </c>
       <c r="D496" t="n">
-        <v>24007</v>
+        <v>25031</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>31.37</v>
+        <v>177.54</v>
       </c>
       <c r="B497" t="n">
-        <v>25326</v>
+        <v>19102</v>
       </c>
       <c r="C497" t="n">
-        <v>33.01</v>
+        <v>179.77</v>
       </c>
       <c r="D497" t="n">
-        <v>24923</v>
+        <v>24063</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>91.42</v>
+        <v>177.66</v>
       </c>
       <c r="B498" t="n">
-        <v>29216</v>
+        <v>18898</v>
       </c>
       <c r="C498" t="n">
-        <v>89.29000000000001</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>23837</v>
+        <v>24918</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>104.86</v>
+        <v>178.36</v>
       </c>
       <c r="B499" t="n">
-        <v>49963</v>
+        <v>17307</v>
       </c>
       <c r="C499" t="n">
-        <v>107.02</v>
+        <v>156.84</v>
       </c>
       <c r="D499" t="n">
-        <v>23920</v>
+        <v>24921</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>141.58</v>
+        <v>179.66</v>
       </c>
       <c r="B500" t="n">
-        <v>26504</v>
+        <v>19058</v>
       </c>
       <c r="C500" t="n">
-        <v>145.92</v>
+        <v>153.25</v>
       </c>
       <c r="D500" t="n">
-        <v>23896</v>
+        <v>23806</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>95.04000000000001</v>
+        <v>179.76</v>
       </c>
       <c r="B501" t="n">
-        <v>33322</v>
+        <v>17948</v>
       </c>
       <c r="C501" t="n">
-        <v>98.58</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>24941</v>
+        <v>23923</v>
       </c>
     </row>
   </sheetData>
